--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T08:25:56+00:00</t>
+    <t>2026-09-14T07:00:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:00:54+00:00</t>
+    <t>2026-09-14T09:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8067" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8068" uniqueCount="901">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:05:35+00:00</t>
+    <t>2026-09-14T11:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2353,7 +2353,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
+    <t>Nur tatsächlich durchgeführte (completed) Prozeduren werden in der e-Diagnose dokumentiert.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -2363,7 +2363,13 @@
 This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/event-status|4.0.1</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -2373,7 +2379,7 @@
 Cancelled Reason</t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
+    <t>Begründung für den Status der Prozedur nicht relevant.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -2412,7 +2418,7 @@
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-code</t>
   </si>
   <si>
     <t>Procedure.code.id</t>
@@ -3836,7 +3842,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="116">
@@ -3844,7 +3850,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="117">
@@ -3860,7 +3866,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="119">
@@ -3868,7 +3874,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="120">
@@ -3998,7 +4004,7 @@
         <v>530</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="137">
@@ -4014,7 +4020,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="139">
@@ -4022,7 +4028,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="140">
@@ -4038,7 +4044,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="142">
@@ -4176,7 +4182,7 @@
         <v>530</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -23425,7 +23431,7 @@
       </c>
       <c r="R184" s="2"/>
       <c r="S184" t="s" s="2">
-        <v>23</v>
+        <v>753</v>
       </c>
       <c r="T184" t="s" s="2">
         <v>23</v>
@@ -23445,9 +23451,11 @@
       <c r="Y184" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="Z184" s="2"/>
+      <c r="Z184" t="s" s="2">
+        <v>754</v>
+      </c>
       <c r="AA184" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AB184" t="s" s="2">
         <v>23</v>
@@ -23485,21 +23493,21 @@
         <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>23</v>
@@ -23514,13 +23522,13 @@
         <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -23549,10 +23557,10 @@
         <v>199</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
@@ -23570,7 +23578,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23590,10 +23598,10 @@
         <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23619,10 +23627,10 @@
         <v>160</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -23652,10 +23660,10 @@
         <v>199</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>23</v>
@@ -23673,7 +23681,7 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>77</v>
@@ -23693,10 +23701,10 @@
         <v>706</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23722,10 +23730,10 @@
         <v>160</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23758,7 +23766,7 @@
       </c>
       <c r="Z187" s="2"/>
       <c r="AA187" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="AB187" t="s" s="2">
         <v>23</v>
@@ -23776,7 +23784,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -23796,10 +23804,10 @@
         <v>706</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23899,10 +23907,10 @@
         <v>706</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24004,10 +24012,10 @@
         <v>706</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24111,10 +24119,10 @@
         <v>706</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24218,10 +24226,10 @@
         <v>706</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24247,10 +24255,10 @@
         <v>227</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -24301,7 +24309,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>85</v>
@@ -24321,10 +24329,10 @@
         <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24353,10 +24361,10 @@
         <v>232</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -24406,7 +24414,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24426,10 +24434,10 @@
         <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24455,13 +24463,13 @@
         <v>239</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24511,7 +24519,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -24531,10 +24539,10 @@
         <v>706</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24560,7 +24568,7 @@
         <v>244</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>246</v>
@@ -24614,7 +24622,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>77</v>
@@ -24634,10 +24642,10 @@
         <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24663,10 +24671,10 @@
         <v>249</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
@@ -24717,7 +24725,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -24737,10 +24745,10 @@
         <v>706</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24766,10 +24774,10 @@
         <v>263</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -24820,7 +24828,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -24840,10 +24848,10 @@
         <v>706</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24943,10 +24951,10 @@
         <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25048,10 +25056,10 @@
         <v>706</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -25155,10 +25163,10 @@
         <v>706</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25184,14 +25192,14 @@
         <v>160</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Q201" t="s" s="2">
         <v>23</v>
@@ -25219,10 +25227,10 @@
         <v>199</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AA201" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AB201" t="s" s="2">
         <v>23</v>
@@ -25240,7 +25248,7 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
@@ -25260,10 +25268,10 @@
         <v>706</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25286,17 +25294,17 @@
         <v>86</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="Q202" t="s" s="2">
         <v>23</v>
@@ -25345,7 +25353,7 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>85</v>
@@ -25365,10 +25373,10 @@
         <v>706</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25391,17 +25399,17 @@
         <v>23</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="Q203" t="s" s="2">
         <v>23</v>
@@ -25450,7 +25458,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
@@ -25470,10 +25478,10 @@
         <v>706</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25496,17 +25504,17 @@
         <v>86</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="Q204" t="s" s="2">
         <v>23</v>
@@ -25555,7 +25563,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25575,10 +25583,10 @@
         <v>706</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25604,13 +25612,13 @@
         <v>160</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -25639,10 +25647,10 @@
         <v>199</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AA205" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AB205" t="s" s="2">
         <v>23</v>
@@ -25660,7 +25668,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25680,10 +25688,10 @@
         <v>706</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25706,16 +25714,16 @@
         <v>86</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
@@ -25765,7 +25773,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25785,10 +25793,10 @@
         <v>706</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25814,13 +25822,13 @@
         <v>160</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" t="s" s="2">
@@ -25870,7 +25878,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -25890,10 +25898,10 @@
         <v>706</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25919,13 +25927,13 @@
         <v>160</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
@@ -25954,10 +25962,10 @@
         <v>199</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AA208" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>23</v>
@@ -25975,7 +25983,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -25995,10 +26003,10 @@
         <v>706</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26021,16 +26029,16 @@
         <v>23</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>499</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" t="s" s="2">
@@ -26080,7 +26088,7 @@
         <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -26100,10 +26108,10 @@
         <v>706</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26129,13 +26137,13 @@
         <v>160</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -26164,7 +26172,7 @@
         <v>199</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>387</v>
@@ -26185,7 +26193,7 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
@@ -26205,10 +26213,10 @@
         <v>706</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26231,17 +26239,17 @@
         <v>23</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="Q211" t="s" s="2">
         <v>23</v>
@@ -26290,7 +26298,7 @@
         <v>23</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>77</v>
@@ -26310,10 +26318,10 @@
         <v>706</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26339,10 +26347,10 @@
         <v>160</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -26372,10 +26380,10 @@
         <v>199</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="AA212" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="AB212" t="s" s="2">
         <v>23</v>
@@ -26393,7 +26401,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -26413,10 +26421,10 @@
         <v>706</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26442,10 +26450,10 @@
         <v>258</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26496,7 +26504,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -26516,10 +26524,10 @@
         <v>706</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26619,10 +26627,10 @@
         <v>706</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26724,10 +26732,10 @@
         <v>706</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26829,10 +26837,10 @@
         <v>706</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26932,10 +26940,10 @@
         <v>706</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27035,10 +27043,10 @@
         <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27064,10 +27072,10 @@
         <v>263</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -27118,7 +27126,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -27138,10 +27146,10 @@
         <v>706</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27241,10 +27249,10 @@
         <v>706</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27346,10 +27354,10 @@
         <v>706</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27453,10 +27461,10 @@
         <v>706</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27482,10 +27490,10 @@
         <v>160</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27515,10 +27523,10 @@
         <v>109</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>23</v>
@@ -27536,7 +27544,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -27556,10 +27564,10 @@
         <v>706</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27582,13 +27590,13 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -27639,7 +27647,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>85</v>
@@ -27659,10 +27667,10 @@
         <v>706</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27685,19 +27693,19 @@
         <v>23</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="P225" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
@@ -27746,7 +27754,7 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
@@ -27766,10 +27774,10 @@
         <v>706</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -27795,13 +27803,13 @@
         <v>160</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -27830,10 +27838,10 @@
         <v>199</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="AA226" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="AB226" t="s" s="2">
         <v>23</v>
@@ -27851,7 +27859,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -27868,7 +27876,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>129</v>
@@ -27900,7 +27908,7 @@
         <v>79</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>272</v>
@@ -27971,7 +27979,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>534</v>
@@ -28074,7 +28082,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>535</v>
@@ -28177,7 +28185,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>547</v>
@@ -28223,7 +28231,7 @@
       </c>
       <c r="R230" s="2"/>
       <c r="S230" t="s" s="2">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>23</v>
@@ -28282,7 +28290,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>553</v>
@@ -28385,7 +28393,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>129</v>
@@ -28488,7 +28496,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>534</v>
@@ -28591,7 +28599,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>535</v>
@@ -28694,7 +28702,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>547</v>
@@ -28740,7 +28748,7 @@
       </c>
       <c r="R235" s="2"/>
       <c r="S235" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>23</v>
@@ -28799,7 +28807,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>553</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:30:22+00:00</t>
+    <t>2026-09-15T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1230,7 +1230,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-codes</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-condition-code</t>
   </si>
   <si>
     <t>Condition.code.id</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7534" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7533" uniqueCount="849">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:16:05+00:00</t>
+    <t>2026-09-16T05:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,13 +644,7 @@
 The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/allergyintolerance-code|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-allergyintolerance-code</t>
   </si>
   <si>
     <t>AllergyIntolerance.code.id</t>
@@ -907,6 +901,9 @@
   </si>
   <si>
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
@@ -2255,7 +2252,7 @@
     <t>Procedure.code</t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur.</t>
+    <t>Prozedurencode der durchgeführten Prozedur; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -2984,7 +2981,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25">
@@ -2992,7 +2989,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26">
@@ -3008,7 +3005,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28">
@@ -3016,7 +3013,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29">
@@ -3078,7 +3075,7 @@
         <v>24</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37">
@@ -3114,7 +3111,7 @@
         <v>32</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42">
@@ -3122,7 +3119,7 @@
         <v>34</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="43">
@@ -3154,7 +3151,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47">
@@ -3162,7 +3159,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="48">
@@ -3178,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="50">
@@ -3194,7 +3191,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52">
@@ -3276,7 +3273,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="63">
@@ -3292,7 +3289,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65">
@@ -3313,26 +3310,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>477</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70">
@@ -3348,7 +3345,7 @@
         <v>2</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="72">
@@ -3356,7 +3353,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="73">
@@ -3372,7 +3369,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="75">
@@ -3380,7 +3377,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="76">
@@ -3442,7 +3439,7 @@
         <v>24</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84">
@@ -3478,7 +3475,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89">
@@ -3486,7 +3483,7 @@
         <v>34</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="90">
@@ -3518,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="94">
@@ -3526,7 +3523,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="95">
@@ -3542,7 +3539,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="97">
@@ -3550,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="98">
@@ -3612,7 +3609,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="106">
@@ -3648,7 +3645,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="111">
@@ -3656,7 +3653,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="112">
@@ -3688,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="116">
@@ -3696,7 +3693,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="117">
@@ -3712,7 +3709,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="119">
@@ -3720,7 +3717,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="120">
@@ -3782,7 +3779,7 @@
         <v>24</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="128">
@@ -3810,7 +3807,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="132">
@@ -3826,7 +3823,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="134">
@@ -3847,10 +3844,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="137">
@@ -3866,7 +3863,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="139">
@@ -3874,7 +3871,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="140">
@@ -3890,7 +3887,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="142">
@@ -3906,7 +3903,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="144">
@@ -3988,7 +3985,7 @@
         <v>30</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155">
@@ -4004,7 +4001,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="157">
@@ -4025,10 +4022,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4064,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="55.875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="58.875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6040,13 +6037,11 @@
         <v>23</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z19" s="2"/>
+      <c r="AA19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AB19" t="s" s="2">
         <v>23</v>
@@ -6084,10 +6079,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -6110,13 +6105,13 @@
         <v>23</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -6167,7 +6162,7 @@
         <v>23</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>77</v>
@@ -6187,10 +6182,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -6216,10 +6211,10 @@
         <v>128</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O21" t="s" s="2">
         <v>150</v>
@@ -6263,7 +6258,7 @@
         <v>131</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE21" t="s" s="2">
         <v>23</v>
@@ -6272,7 +6267,7 @@
         <v>132</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>77</v>
@@ -6292,10 +6287,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -6303,10 +6298,10 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>23</v>
@@ -6318,19 +6313,19 @@
         <v>86</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="P22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>23</v>
@@ -6379,7 +6374,7 @@
         <v>23</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>77</v>
@@ -6399,10 +6394,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -6425,19 +6420,19 @@
         <v>86</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="P23" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="P23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>23</v>
@@ -6486,7 +6481,7 @@
         <v>23</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>77</v>
@@ -6506,14 +6501,14 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -6532,13 +6527,13 @@
         <v>86</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -6589,7 +6584,7 @@
         <v>23</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>85</v>
@@ -6609,10 +6604,10 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -6635,13 +6630,13 @@
         <v>23</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
@@ -6692,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>77</v>
@@ -6712,10 +6707,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -6738,13 +6733,13 @@
         <v>23</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -6795,7 +6790,7 @@
         <v>23</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>77</v>
@@ -6815,10 +6810,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -6841,13 +6836,13 @@
         <v>23</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -6898,7 +6893,7 @@
         <v>23</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>77</v>
@@ -6918,14 +6913,14 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
@@ -6944,13 +6939,13 @@
         <v>23</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
@@ -7001,7 +6996,7 @@
         <v>23</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>77</v>
@@ -7021,14 +7016,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -7047,16 +7042,16 @@
         <v>86</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
@@ -7106,7 +7101,7 @@
         <v>23</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>77</v>
@@ -7126,10 +7121,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -7152,16 +7147,16 @@
         <v>23</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -7211,7 +7206,7 @@
         <v>23</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>77</v>
@@ -7231,10 +7226,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -7257,16 +7252,16 @@
         <v>23</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -7316,7 +7311,7 @@
         <v>23</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>77</v>
@@ -7336,10 +7331,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -7362,13 +7357,13 @@
         <v>23</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -7419,7 +7414,7 @@
         <v>23</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>77</v>
@@ -7439,10 +7434,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -7465,13 +7460,13 @@
         <v>23</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -7522,7 +7517,7 @@
         <v>23</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>77</v>
@@ -7542,10 +7537,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -7623,7 +7618,7 @@
         <v>132</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>77</v>
@@ -7643,13 +7638,13 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="D35" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="E35" t="s" s="2">
         <v>23</v>
@@ -7671,13 +7666,13 @@
         <v>23</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -7728,7 +7723,7 @@
         <v>23</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>77</v>
@@ -7748,14 +7743,14 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
@@ -7777,10 +7772,10 @@
         <v>128</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>150</v>
@@ -7835,7 +7830,7 @@
         <v>23</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>77</v>
@@ -7855,10 +7850,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -7884,13 +7879,13 @@
         <v>160</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" t="s" s="2">
@@ -7916,14 +7911,14 @@
         <v>23</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AA37" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AB37" t="s" s="2">
         <v>23</v>
       </c>
@@ -7940,7 +7935,7 @@
         <v>23</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>77</v>
@@ -7960,14 +7955,14 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" t="s" s="2">
@@ -7989,13 +7984,13 @@
         <v>160</v>
       </c>
       <c r="M38" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" t="s" s="2">
@@ -8021,14 +8016,14 @@
         <v>23</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AA38" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AB38" t="s" s="2">
         <v>23</v>
       </c>
@@ -8045,7 +8040,7 @@
         <v>23</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>85</v>
@@ -8065,14 +8060,14 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
@@ -8091,16 +8086,16 @@
         <v>23</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M39" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
@@ -8150,7 +8145,7 @@
         <v>23</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>77</v>
@@ -8170,10 +8165,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -8196,13 +8191,13 @@
         <v>23</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -8253,7 +8248,7 @@
         <v>23</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>77</v>
@@ -8273,10 +8268,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -8302,13 +8297,13 @@
         <v>105</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
@@ -8337,11 +8332,11 @@
         <v>164</v>
       </c>
       <c r="Z41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AA41" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AA41" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AB41" t="s" s="2">
         <v>23</v>
       </c>
@@ -8358,7 +8353,7 @@
         <v>23</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>77</v>
@@ -8378,10 +8373,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -8407,13 +8402,13 @@
         <v>160</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
@@ -8439,14 +8434,14 @@
         <v>23</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AA42" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AB42" t="s" s="2">
         <v>23</v>
       </c>
@@ -8463,7 +8458,7 @@
         <v>23</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>77</v>
@@ -8483,10 +8478,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -8509,16 +8504,16 @@
         <v>23</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" t="s" s="2">
@@ -8568,7 +8563,7 @@
         <v>23</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>77</v>
@@ -8588,10 +8583,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -8614,13 +8609,13 @@
         <v>23</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
@@ -8671,7 +8666,7 @@
         <v>23</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>77</v>
@@ -8691,10 +8686,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -8720,10 +8715,10 @@
         <v>128</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>150</v>
@@ -8767,7 +8762,7 @@
         <v>131</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE45" t="s" s="2">
         <v>23</v>
@@ -8776,7 +8771,7 @@
         <v>132</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>77</v>
@@ -8796,10 +8791,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -8822,16 +8817,16 @@
         <v>86</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
@@ -8881,7 +8876,7 @@
         <v>23</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>77</v>
@@ -8901,10 +8896,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -8927,13 +8922,13 @@
         <v>86</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -8984,7 +8979,7 @@
         <v>23</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>77</v>
@@ -9004,10 +8999,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -9030,13 +9025,13 @@
         <v>86</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
@@ -9087,7 +9082,7 @@
         <v>23</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>85</v>
@@ -9104,13 +9099,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -9136,10 +9131,10 @@
         <v>79</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -9190,7 +9185,7 @@
         <v>23</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>77</v>
@@ -9202,18 +9197,18 @@
         <v>23</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -9312,13 +9307,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -9415,13 +9410,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -9520,13 +9515,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -9625,13 +9620,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -9730,13 +9725,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -9835,13 +9830,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -9936,13 +9931,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>136</v>
@@ -10041,13 +10036,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>142</v>
@@ -10146,13 +10141,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -10253,13 +10248,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -10285,16 +10280,16 @@
         <v>154</v>
       </c>
       <c r="M60" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>157</v>
       </c>
       <c r="P60" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q60" t="s" s="2">
         <v>23</v>
@@ -10343,7 +10338,7 @@
         <v>23</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>77</v>
@@ -10360,13 +10355,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -10392,13 +10387,13 @@
         <v>160</v>
       </c>
       <c r="M61" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" t="s" s="2">
@@ -10427,37 +10422,37 @@
         <v>164</v>
       </c>
       <c r="Z61" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA61" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AA61" t="s" s="2">
+      <c r="AB61" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>97</v>
@@ -10465,13 +10460,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -10497,13 +10492,13 @@
         <v>160</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" t="s" s="2">
@@ -10532,37 +10527,37 @@
         <v>164</v>
       </c>
       <c r="Z62" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AA62" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AA62" t="s" s="2">
+      <c r="AB62" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>97</v>
@@ -10570,13 +10565,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -10602,13 +10597,13 @@
         <v>160</v>
       </c>
       <c r="M63" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
@@ -10634,14 +10629,14 @@
         <v>23</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AA63" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AB63" t="s" s="2">
         <v>23</v>
       </c>
@@ -10658,7 +10653,7 @@
         <v>23</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>77</v>
@@ -10675,13 +10670,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -10707,13 +10702,13 @@
         <v>160</v>
       </c>
       <c r="M64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
@@ -10742,10 +10737,10 @@
         <v>109</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AB64" t="s" s="2">
         <v>23</v>
@@ -10763,7 +10758,7 @@
         <v>23</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>77</v>
@@ -10780,17 +10775,17 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
@@ -10812,14 +10807,14 @@
         <v>160</v>
       </c>
       <c r="M65" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>23</v>
@@ -10848,7 +10843,7 @@
       </c>
       <c r="Z65" s="2"/>
       <c r="AA65" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>23</v>
@@ -10866,7 +10861,7 @@
         <v>23</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>77</v>
@@ -10883,13 +10878,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -10912,13 +10907,13 @@
         <v>23</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -10969,7 +10964,7 @@
         <v>23</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>77</v>
@@ -10986,13 +10981,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -11018,10 +11013,10 @@
         <v>128</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>150</v>
@@ -11065,7 +11060,7 @@
         <v>131</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE67" t="s" s="2">
         <v>23</v>
@@ -11074,7 +11069,7 @@
         <v>132</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>77</v>
@@ -11091,13 +11086,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -11120,19 +11115,19 @@
         <v>86</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="P68" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="Q68" t="s" s="2">
         <v>23</v>
@@ -11181,7 +11176,7 @@
         <v>23</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>77</v>
@@ -11198,13 +11193,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -11227,19 +11222,19 @@
         <v>86</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M69" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O69" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="P69" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="Q69" t="s" s="2">
         <v>23</v>
@@ -11288,7 +11283,7 @@
         <v>23</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>77</v>
@@ -11305,13 +11300,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -11337,13 +11332,13 @@
         <v>160</v>
       </c>
       <c r="M70" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -11369,14 +11364,14 @@
         <v>23</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z70" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA70" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AA70" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AB70" t="s" s="2">
         <v>23</v>
       </c>
@@ -11393,7 +11388,7 @@
         <v>23</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>77</v>
@@ -11410,17 +11405,17 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -11439,17 +11434,17 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M71" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q71" t="s" s="2">
         <v>23</v>
@@ -11498,7 +11493,7 @@
         <v>23</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>85</v>
@@ -11515,13 +11510,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -11544,16 +11539,16 @@
         <v>86</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N72" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
@@ -11603,7 +11598,7 @@
         <v>23</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>77</v>
@@ -11620,13 +11615,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -11649,16 +11644,16 @@
         <v>86</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M73" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
@@ -11708,7 +11703,7 @@
         <v>23</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>77</v>
@@ -11725,13 +11720,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -11754,16 +11749,16 @@
         <v>23</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
@@ -11813,7 +11808,7 @@
         <v>23</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>77</v>
@@ -11822,7 +11817,7 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>97</v>
@@ -11830,13 +11825,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -11859,13 +11854,13 @@
         <v>86</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M75" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -11916,7 +11911,7 @@
         <v>23</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>77</v>
@@ -11933,13 +11928,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11962,13 +11957,13 @@
         <v>86</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
@@ -12019,7 +12014,7 @@
         <v>23</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>77</v>
@@ -12036,13 +12031,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -12065,13 +12060,13 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
@@ -12122,7 +12117,7 @@
         <v>23</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>77</v>
@@ -12139,13 +12134,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -12168,13 +12163,13 @@
         <v>23</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M78" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -12225,7 +12220,7 @@
         <v>23</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>77</v>
@@ -12237,18 +12232,18 @@
         <v>23</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -12271,13 +12266,13 @@
         <v>23</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -12328,7 +12323,7 @@
         <v>23</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>77</v>
@@ -12345,13 +12340,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -12377,10 +12372,10 @@
         <v>128</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>150</v>
@@ -12433,7 +12428,7 @@
         <v>23</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>77</v>
@@ -12450,17 +12445,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" t="s" s="2">
@@ -12482,10 +12477,10 @@
         <v>128</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>150</v>
@@ -12540,7 +12535,7 @@
         <v>23</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>77</v>
@@ -12557,13 +12552,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -12589,10 +12584,10 @@
         <v>160</v>
       </c>
       <c r="M82" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -12619,40 +12614,40 @@
         <v>23</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z82" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AA82" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AA82" t="s" s="2">
+      <c r="AB82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>97</v>
@@ -12660,13 +12655,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -12689,13 +12684,13 @@
         <v>23</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -12746,7 +12741,7 @@
         <v>23</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>77</v>
@@ -12755,7 +12750,7 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>97</v>
@@ -12763,13 +12758,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -12795,10 +12790,10 @@
         <v>160</v>
       </c>
       <c r="M84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -12825,14 +12820,14 @@
         <v>23</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z84" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AA84" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AA84" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AB84" t="s" s="2">
         <v>23</v>
       </c>
@@ -12849,7 +12844,7 @@
         <v>23</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>77</v>
@@ -12866,13 +12861,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -12895,16 +12890,16 @@
         <v>23</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
@@ -12954,7 +12949,7 @@
         <v>23</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>77</v>
@@ -12966,18 +12961,18 @@
         <v>23</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -13000,13 +12995,13 @@
         <v>23</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -13057,7 +13052,7 @@
         <v>23</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>77</v>
@@ -13074,13 +13069,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -13106,10 +13101,10 @@
         <v>128</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>150</v>
@@ -13162,7 +13157,7 @@
         <v>23</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>77</v>
@@ -13179,17 +13174,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
@@ -13211,10 +13206,10 @@
         <v>128</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>150</v>
@@ -13269,7 +13264,7 @@
         <v>23</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>77</v>
@@ -13286,13 +13281,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -13318,10 +13313,10 @@
         <v>160</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -13348,14 +13343,14 @@
         <v>23</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z89" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AA89" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AA89" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AB89" t="s" s="2">
         <v>23</v>
       </c>
@@ -13372,7 +13367,7 @@
         <v>23</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>77</v>
@@ -13381,7 +13376,7 @@
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>97</v>
@@ -13389,13 +13384,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -13418,13 +13413,13 @@
         <v>86</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -13475,7 +13470,7 @@
         <v>23</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>77</v>
@@ -13484,7 +13479,7 @@
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>97</v>
@@ -13492,13 +13487,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -13521,13 +13516,13 @@
         <v>23</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M91" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -13578,7 +13573,7 @@
         <v>23</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>77</v>
@@ -13595,13 +13590,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -13624,13 +13619,13 @@
         <v>23</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -13681,7 +13676,7 @@
         <v>23</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
@@ -13698,13 +13693,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -13730,10 +13725,10 @@
         <v>128</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>150</v>
@@ -13777,7 +13772,7 @@
         <v>131</v>
       </c>
       <c r="AD93" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE93" t="s" s="2">
         <v>23</v>
@@ -13786,7 +13781,7 @@
         <v>132</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -13803,13 +13798,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -13832,16 +13827,16 @@
         <v>86</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P94" s="2"/>
       <c r="Q94" t="s" s="2">
@@ -13891,7 +13886,7 @@
         <v>23</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>77</v>
@@ -13908,13 +13903,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13937,13 +13932,13 @@
         <v>86</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M95" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -13994,7 +13989,7 @@
         <v>23</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>77</v>
@@ -14011,13 +14006,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -14040,13 +14035,13 @@
         <v>86</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -14097,7 +14092,7 @@
         <v>23</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -14114,7 +14109,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>129</v>
@@ -14217,13 +14212,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -14246,13 +14241,13 @@
         <v>23</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -14303,7 +14298,7 @@
         <v>23</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>77</v>
@@ -14320,13 +14315,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -14334,7 +14329,7 @@
       </c>
       <c r="F99" s="2"/>
       <c r="G99" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -14397,7 +14392,7 @@
         <v>131</v>
       </c>
       <c r="AD99" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE99" t="s" s="2">
         <v>23</v>
@@ -14406,7 +14401,7 @@
         <v>132</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>77</v>
@@ -14423,16 +14418,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B100" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D100" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="E100" t="s" s="2">
         <v>23</v>
@@ -14511,7 +14506,7 @@
         <v>23</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -14528,13 +14523,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B101" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14557,13 +14552,13 @@
         <v>23</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -14614,7 +14609,7 @@
         <v>23</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>77</v>
@@ -14631,13 +14626,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B102" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -14708,7 +14703,7 @@
         <v>131</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE102" t="s" s="2">
         <v>23</v>
@@ -14717,7 +14712,7 @@
         <v>132</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>77</v>
@@ -14734,13 +14729,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B103" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14766,13 +14761,13 @@
         <v>99</v>
       </c>
       <c r="M103" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -14780,7 +14775,7 @@
       </c>
       <c r="R103" s="2"/>
       <c r="S103" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>23</v>
@@ -14822,7 +14817,7 @@
         <v>23</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>85</v>
@@ -14839,13 +14834,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B104" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14868,13 +14863,13 @@
         <v>23</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -14925,7 +14920,7 @@
         <v>23</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>77</v>
@@ -14942,16 +14937,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B105" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D105" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="D105" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="E105" t="s" s="2">
         <v>23</v>
@@ -15030,7 +15025,7 @@
         <v>23</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>77</v>
@@ -15047,13 +15042,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -15076,13 +15071,13 @@
         <v>23</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -15133,7 +15128,7 @@
         <v>23</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>77</v>
@@ -15150,13 +15145,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -15227,7 +15222,7 @@
         <v>131</v>
       </c>
       <c r="AD107" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE107" t="s" s="2">
         <v>23</v>
@@ -15236,7 +15231,7 @@
         <v>132</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -15253,13 +15248,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -15285,13 +15280,13 @@
         <v>99</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -15299,7 +15294,7 @@
       </c>
       <c r="R108" s="2"/>
       <c r="S108" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>23</v>
@@ -15341,7 +15336,7 @@
         <v>23</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>85</v>
@@ -15358,13 +15353,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -15387,13 +15382,13 @@
         <v>23</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M109" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -15444,7 +15439,7 @@
         <v>23</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>77</v>
@@ -15461,16 +15456,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B110" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D110" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="D110" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="E110" t="s" s="2">
         <v>23</v>
@@ -15549,7 +15544,7 @@
         <v>23</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>77</v>
@@ -15566,13 +15561,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -15595,13 +15590,13 @@
         <v>23</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -15652,7 +15647,7 @@
         <v>23</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>77</v>
@@ -15669,13 +15664,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15746,7 +15741,7 @@
         <v>131</v>
       </c>
       <c r="AD112" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE112" t="s" s="2">
         <v>23</v>
@@ -15755,7 +15750,7 @@
         <v>132</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>77</v>
@@ -15772,13 +15767,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15804,13 +15799,13 @@
         <v>99</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
@@ -15818,7 +15813,7 @@
       </c>
       <c r="R113" s="2"/>
       <c r="S113" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>23</v>
@@ -15860,7 +15855,7 @@
         <v>23</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>85</v>
@@ -15877,13 +15872,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15906,13 +15901,13 @@
         <v>23</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M114" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N114" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
@@ -15963,7 +15958,7 @@
         <v>23</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>77</v>
@@ -15980,13 +15975,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -16012,13 +16007,13 @@
         <v>99</v>
       </c>
       <c r="M115" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P115" s="2"/>
       <c r="Q115" t="s" s="2">
@@ -16026,7 +16021,7 @@
       </c>
       <c r="R115" s="2"/>
       <c r="S115" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>23</v>
@@ -16068,7 +16063,7 @@
         <v>23</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>85</v>
@@ -16085,13 +16080,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -16114,13 +16109,13 @@
         <v>23</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M116" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -16171,7 +16166,7 @@
         <v>23</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>77</v>
@@ -16188,17 +16183,17 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
@@ -16220,10 +16215,10 @@
         <v>79</v>
       </c>
       <c r="M117" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N117" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -16274,7 +16269,7 @@
         <v>23</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>77</v>
@@ -16286,18 +16281,18 @@
         <v>23</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -16396,13 +16391,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16499,13 +16494,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16604,13 +16599,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16709,13 +16704,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16814,13 +16809,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16919,13 +16914,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16951,10 +16946,10 @@
         <v>128</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>150</v>
@@ -17024,13 +17019,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -17131,13 +17126,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -17163,10 +17158,10 @@
         <v>154</v>
       </c>
       <c r="M126" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -17217,7 +17212,7 @@
         <v>23</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>77</v>
@@ -17234,13 +17229,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17266,13 +17261,13 @@
         <v>105</v>
       </c>
       <c r="M127" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P127" s="2"/>
       <c r="Q127" t="s" s="2">
@@ -17280,7 +17275,7 @@
       </c>
       <c r="R127" s="2"/>
       <c r="S127" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>23</v>
@@ -17301,11 +17296,11 @@
         <v>164</v>
       </c>
       <c r="Z127" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AA127" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AA127" t="s" s="2">
-        <v>543</v>
-      </c>
       <c r="AB127" t="s" s="2">
         <v>23</v>
       </c>
@@ -17322,7 +17317,7 @@
         <v>23</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>85</v>
@@ -17339,13 +17334,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17371,23 +17366,23 @@
         <v>105</v>
       </c>
       <c r="M128" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="O128" t="s" s="2">
+      <c r="P128" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R128" s="2"/>
       <c r="S128" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>23</v>
@@ -17408,11 +17403,11 @@
         <v>164</v>
       </c>
       <c r="Z128" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AA128" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AA128" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="AB128" t="s" s="2">
         <v>23</v>
       </c>
@@ -17429,7 +17424,7 @@
         <v>23</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>85</v>
@@ -17446,13 +17441,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17475,17 +17470,17 @@
         <v>86</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M129" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>23</v>
@@ -17498,7 +17493,7 @@
         <v>23</v>
       </c>
       <c r="U129" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="V129" t="s" s="2">
         <v>23</v>
@@ -17534,7 +17529,7 @@
         <v>23</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>77</v>
@@ -17551,13 +17546,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17583,16 +17578,16 @@
         <v>160</v>
       </c>
       <c r="M130" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="O130" t="s" s="2">
+      <c r="P130" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="Q130" t="s" s="2">
         <v>23</v>
@@ -17621,7 +17616,7 @@
       </c>
       <c r="Z130" s="2"/>
       <c r="AA130" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AB130" t="s" s="2">
         <v>23</v>
@@ -17639,7 +17634,7 @@
         <v>23</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>77</v>
@@ -17656,13 +17651,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17685,19 +17680,19 @@
         <v>86</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="O131" t="s" s="2">
+      <c r="P131" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="Q131" t="s" s="2">
         <v>23</v>
@@ -17746,7 +17741,7 @@
         <v>23</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>77</v>
@@ -17763,13 +17758,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17792,13 +17787,13 @@
         <v>23</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M132" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -17849,7 +17844,7 @@
         <v>23</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>77</v>
@@ -17866,13 +17861,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17895,19 +17890,19 @@
         <v>86</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M133" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="O133" t="s" s="2">
+      <c r="P133" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="P133" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="Q133" t="s" s="2">
         <v>23</v>
@@ -17956,7 +17951,7 @@
         <v>23</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>77</v>
@@ -17973,17 +17968,17 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" t="s" s="2">
@@ -18002,19 +17997,19 @@
         <v>86</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="O134" t="s" s="2">
+      <c r="P134" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="Q134" t="s" s="2">
         <v>23</v>
@@ -18063,7 +18058,7 @@
         <v>23</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>77</v>
@@ -18080,13 +18075,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -18112,16 +18107,16 @@
         <v>160</v>
       </c>
       <c r="M135" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="O135" t="s" s="2">
+      <c r="P135" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="Q135" t="s" s="2">
         <v>23</v>
@@ -18149,11 +18144,11 @@
         <v>109</v>
       </c>
       <c r="Z135" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AA135" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AA135" t="s" s="2">
-        <v>588</v>
-      </c>
       <c r="AB135" t="s" s="2">
         <v>23</v>
       </c>
@@ -18170,7 +18165,7 @@
         <v>23</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>77</v>
@@ -18187,13 +18182,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -18216,13 +18211,13 @@
         <v>23</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M136" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N136" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -18273,7 +18268,7 @@
         <v>23</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>77</v>
@@ -18290,13 +18285,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18319,16 +18314,16 @@
         <v>23</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M137" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N137" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="P137" s="2"/>
       <c r="Q137" t="s" s="2">
@@ -18378,7 +18373,7 @@
         <v>23</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>77</v>
@@ -18387,7 +18382,7 @@
         <v>78</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>97</v>
@@ -18395,13 +18390,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18424,13 +18419,13 @@
         <v>23</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -18481,7 +18476,7 @@
         <v>23</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>77</v>
@@ -18498,13 +18493,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18530,10 +18525,10 @@
         <v>128</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O139" t="s" s="2">
         <v>150</v>
@@ -18586,7 +18581,7 @@
         <v>23</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>77</v>
@@ -18603,17 +18598,17 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s" s="2">
@@ -18635,10 +18630,10 @@
         <v>128</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O140" t="s" s="2">
         <v>150</v>
@@ -18693,7 +18688,7 @@
         <v>23</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>77</v>
@@ -18710,13 +18705,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18742,16 +18737,16 @@
         <v>160</v>
       </c>
       <c r="M141" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="O141" t="s" s="2">
+      <c r="P141" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="Q141" t="s" s="2">
         <v>23</v>
@@ -18776,14 +18771,14 @@
         <v>23</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z141" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AA141" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="AA141" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="AB141" t="s" s="2">
         <v>23</v>
       </c>
@@ -18800,7 +18795,7 @@
         <v>23</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>77</v>
@@ -18817,13 +18812,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18846,79 +18841,79 @@
         <v>23</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N142" t="s" s="2">
+      <c r="O142" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="O142" t="s" s="2">
+      <c r="P142" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="P142" t="s" s="2">
+      <c r="Q142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R142" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="Q142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R142" t="s" s="2">
+      <c r="S142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>97</v>
@@ -18926,13 +18921,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18955,17 +18950,17 @@
         <v>23</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q143" t="s" s="2">
         <v>23</v>
@@ -19014,7 +19009,7 @@
         <v>23</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>77</v>
@@ -19031,13 +19026,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19060,13 +19055,13 @@
         <v>23</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -19117,7 +19112,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>85</v>
@@ -19134,13 +19129,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19163,13 +19158,13 @@
         <v>23</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -19220,7 +19215,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>77</v>
@@ -19237,13 +19232,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19269,10 +19264,10 @@
         <v>128</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O146" t="s" s="2">
         <v>150</v>
@@ -19316,7 +19311,7 @@
         <v>131</v>
       </c>
       <c r="AD146" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE146" t="s" s="2">
         <v>23</v>
@@ -19325,7 +19320,7 @@
         <v>132</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>77</v>
@@ -19342,13 +19337,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19371,16 +19366,16 @@
         <v>86</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="P147" s="2"/>
       <c r="Q147" t="s" s="2">
@@ -19430,16 +19425,16 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AH147" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI147" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ147" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>97</v>
@@ -19447,13 +19442,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19479,13 +19474,13 @@
         <v>99</v>
       </c>
       <c r="M148" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P148" s="2"/>
       <c r="Q148" t="s" s="2">
@@ -19511,31 +19506,31 @@
         <v>23</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Z148" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA148" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AA148" t="s" s="2">
+      <c r="AB148" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG148" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -19552,13 +19547,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19584,13 +19579,13 @@
         <v>154</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="P149" s="2"/>
       <c r="Q149" t="s" s="2">
@@ -19640,7 +19635,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -19657,13 +19652,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19686,16 +19681,16 @@
         <v>86</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M150" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="P150" s="2"/>
       <c r="Q150" t="s" s="2">
@@ -19745,7 +19740,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -19762,13 +19757,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19794,16 +19789,16 @@
         <v>160</v>
       </c>
       <c r="M151" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="O151" t="s" s="2">
+      <c r="P151" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -19832,7 +19827,7 @@
       </c>
       <c r="Z151" s="2"/>
       <c r="AA151" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AB151" t="s" s="2">
         <v>23</v>
@@ -19850,7 +19845,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -19859,7 +19854,7 @@
         <v>85</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>97</v>
@@ -19867,13 +19862,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19899,10 +19894,10 @@
         <v>79</v>
       </c>
       <c r="M152" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -19953,7 +19948,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -19965,18 +19960,18 @@
         <v>23</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -20075,13 +20070,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20178,13 +20173,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -20283,13 +20278,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20388,13 +20383,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20493,13 +20488,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20598,13 +20593,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20699,13 +20694,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>136</v>
@@ -20804,13 +20799,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>142</v>
@@ -20909,13 +20904,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21016,13 +21011,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21048,16 +21043,16 @@
         <v>154</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N163" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O163" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="O163" t="s" s="2">
+      <c r="P163" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="P163" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="Q163" t="s" s="2">
         <v>23</v>
@@ -21106,7 +21101,7 @@
         <v>23</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>77</v>
@@ -21123,13 +21118,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21152,13 +21147,13 @@
         <v>86</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -21209,7 +21204,7 @@
         <v>23</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>77</v>
@@ -21226,13 +21221,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21258,13 +21253,13 @@
         <v>99</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21314,7 +21309,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -21331,17 +21326,17 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" t="s" s="2">
@@ -21360,13 +21355,13 @@
         <v>86</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -21417,7 +21412,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -21434,17 +21429,17 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" t="s" s="2">
@@ -21463,16 +21458,16 @@
         <v>86</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -21522,7 +21517,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -21539,13 +21534,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21571,13 +21566,13 @@
         <v>105</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -21585,7 +21580,7 @@
       </c>
       <c r="R168" s="2"/>
       <c r="S168" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>23</v>
@@ -21606,11 +21601,11 @@
         <v>164</v>
       </c>
       <c r="Z168" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AA168" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="AA168" t="s" s="2">
-        <v>703</v>
-      </c>
       <c r="AB168" t="s" s="2">
         <v>23</v>
       </c>
@@ -21627,7 +21622,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>85</v>
@@ -21644,17 +21639,17 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" t="s" s="2">
@@ -21676,13 +21671,13 @@
         <v>160</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
@@ -21708,14 +21703,14 @@
         <v>23</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z169" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AA169" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="AA169" t="s" s="2">
-        <v>710</v>
-      </c>
       <c r="AB169" t="s" s="2">
         <v>23</v>
       </c>
@@ -21732,7 +21727,7 @@
         <v>23</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>77</v>
@@ -21749,13 +21744,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21781,10 +21776,10 @@
         <v>160</v>
       </c>
       <c r="M170" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -21811,14 +21806,14 @@
         <v>23</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z170" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AA170" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="AA170" t="s" s="2">
-        <v>715</v>
-      </c>
       <c r="AB170" t="s" s="2">
         <v>23</v>
       </c>
@@ -21835,7 +21830,7 @@
         <v>23</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>77</v>
@@ -21852,17 +21847,17 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" t="s" s="2">
@@ -21884,14 +21879,14 @@
         <v>160</v>
       </c>
       <c r="M171" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="N171" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q171" t="s" s="2">
         <v>23</v>
@@ -21920,7 +21915,7 @@
       </c>
       <c r="Z171" s="2"/>
       <c r="AA171" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AB171" t="s" s="2">
         <v>23</v>
@@ -21938,7 +21933,7 @@
         <v>23</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>77</v>
@@ -21955,13 +21950,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21984,13 +21979,13 @@
         <v>23</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -22041,7 +22036,7 @@
         <v>23</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>77</v>
@@ -22058,13 +22053,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22090,10 +22085,10 @@
         <v>128</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>150</v>
@@ -22137,7 +22132,7 @@
         <v>131</v>
       </c>
       <c r="AD173" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE173" t="s" s="2">
         <v>23</v>
@@ -22146,7 +22141,7 @@
         <v>132</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>77</v>
@@ -22163,13 +22158,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22192,19 +22187,19 @@
         <v>86</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N174" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="O174" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="N174" t="s" s="2">
+      <c r="P174" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="P174" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="Q174" t="s" s="2">
         <v>23</v>
@@ -22253,7 +22248,7 @@
         <v>23</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>77</v>
@@ -22270,13 +22265,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22299,19 +22294,19 @@
         <v>86</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M175" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O175" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="P175" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="P175" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="Q175" t="s" s="2">
         <v>23</v>
@@ -22360,7 +22355,7 @@
         <v>23</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>77</v>
@@ -22377,17 +22372,17 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" t="s" s="2">
@@ -22406,13 +22401,13 @@
         <v>86</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M176" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="N176" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
@@ -22463,7 +22458,7 @@
         <v>23</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>85</v>
@@ -22480,13 +22475,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22509,16 +22504,16 @@
         <v>86</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N177" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O177" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
@@ -22568,7 +22563,7 @@
         <v>23</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>77</v>
@@ -22585,13 +22580,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -22614,16 +22609,16 @@
         <v>86</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M178" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="N178" t="s" s="2">
+      <c r="O178" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="P178" s="2"/>
       <c r="Q178" t="s" s="2">
@@ -22673,7 +22668,7 @@
         <v>23</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>77</v>
@@ -22690,13 +22685,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22719,13 +22714,13 @@
         <v>86</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
@@ -22776,7 +22771,7 @@
         <v>23</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>77</v>
@@ -22793,13 +22788,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -22822,13 +22817,13 @@
         <v>86</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M180" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="N180" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -22879,7 +22874,7 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
@@ -22896,13 +22891,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22925,13 +22920,13 @@
         <v>86</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M181" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
@@ -22982,7 +22977,7 @@
         <v>23</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -22999,13 +22994,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -23028,13 +23023,13 @@
         <v>23</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23085,7 +23080,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -23102,13 +23097,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -23134,10 +23129,10 @@
         <v>128</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O183" t="s" s="2">
         <v>150</v>
@@ -23190,7 +23185,7 @@
         <v>23</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>77</v>
@@ -23207,17 +23202,17 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" t="s" s="2">
@@ -23239,10 +23234,10 @@
         <v>128</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O184" t="s" s="2">
         <v>150</v>
@@ -23297,7 +23292,7 @@
         <v>23</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>77</v>
@@ -23314,13 +23309,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -23346,14 +23341,14 @@
         <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="N185" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q185" t="s" s="2">
         <v>23</v>
@@ -23378,14 +23373,14 @@
         <v>23</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z185" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AA185" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="AA185" t="s" s="2">
-        <v>750</v>
-      </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
       </c>
@@ -23402,7 +23397,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23419,13 +23414,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23448,17 +23443,17 @@
         <v>86</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="Q186" t="s" s="2">
         <v>23</v>
@@ -23507,7 +23502,7 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>85</v>
@@ -23524,13 +23519,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23553,17 +23548,17 @@
         <v>23</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="Q187" t="s" s="2">
         <v>23</v>
@@ -23612,7 +23607,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -23629,13 +23624,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23658,17 +23653,17 @@
         <v>86</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="Q188" t="s" s="2">
         <v>23</v>
@@ -23717,7 +23712,7 @@
         <v>23</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>77</v>
@@ -23734,13 +23729,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -23766,13 +23761,13 @@
         <v>160</v>
       </c>
       <c r="M189" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="N189" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="N189" t="s" s="2">
+      <c r="O189" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="P189" s="2"/>
       <c r="Q189" t="s" s="2">
@@ -23798,14 +23793,14 @@
         <v>23</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z189" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AA189" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="AA189" t="s" s="2">
-        <v>771</v>
-      </c>
       <c r="AB189" t="s" s="2">
         <v>23</v>
       </c>
@@ -23822,7 +23817,7 @@
         <v>23</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>77</v>
@@ -23839,13 +23834,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -23868,16 +23863,16 @@
         <v>86</v>
       </c>
       <c r="L190" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="M190" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="M190" t="s" s="2">
+      <c r="N190" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="N190" t="s" s="2">
+      <c r="O190" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="P190" s="2"/>
       <c r="Q190" t="s" s="2">
@@ -23927,7 +23922,7 @@
         <v>23</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>77</v>
@@ -23944,13 +23939,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -23976,13 +23971,13 @@
         <v>160</v>
       </c>
       <c r="M191" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="N191" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="N191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="P191" s="2"/>
       <c r="Q191" t="s" s="2">
@@ -24008,14 +24003,14 @@
         <v>23</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z191" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA191" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AA191" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AB191" t="s" s="2">
         <v>23</v>
       </c>
@@ -24032,7 +24027,7 @@
         <v>23</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>77</v>
@@ -24049,13 +24044,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24081,13 +24076,13 @@
         <v>160</v>
       </c>
       <c r="M192" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N192" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="N192" t="s" s="2">
+      <c r="O192" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="P192" s="2"/>
       <c r="Q192" t="s" s="2">
@@ -24113,14 +24108,14 @@
         <v>23</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z192" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AA192" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="AA192" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AB192" t="s" s="2">
         <v>23</v>
       </c>
@@ -24137,7 +24132,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>77</v>
@@ -24154,13 +24149,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24183,16 +24178,16 @@
         <v>23</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N193" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="M193" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N193" t="s" s="2">
+      <c r="O193" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -24242,7 +24237,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24259,13 +24254,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24291,13 +24286,13 @@
         <v>160</v>
       </c>
       <c r="M194" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>792</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24323,14 +24318,14 @@
         <v>23</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z194" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AA194" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AA194" t="s" s="2">
-        <v>796</v>
-      </c>
       <c r="AB194" t="s" s="2">
         <v>23</v>
       </c>
@@ -24347,7 +24342,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -24364,13 +24359,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24393,17 +24388,17 @@
         <v>23</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="Q195" t="s" s="2">
         <v>23</v>
@@ -24452,7 +24447,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>77</v>
@@ -24469,13 +24464,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24501,10 +24496,10 @@
         <v>160</v>
       </c>
       <c r="M196" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N196" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
@@ -24531,14 +24526,14 @@
         <v>23</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z196" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AA196" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="AA196" t="s" s="2">
-        <v>806</v>
-      </c>
       <c r="AB196" t="s" s="2">
         <v>23</v>
       </c>
@@ -24555,7 +24550,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -24572,13 +24567,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24601,13 +24596,13 @@
         <v>23</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M197" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -24658,7 +24653,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -24675,13 +24670,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24704,13 +24699,13 @@
         <v>23</v>
       </c>
       <c r="L198" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M198" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N198" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
@@ -24761,7 +24756,7 @@
         <v>23</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>77</v>
@@ -24778,13 +24773,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -24810,10 +24805,10 @@
         <v>128</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O199" t="s" s="2">
         <v>150</v>
@@ -24857,7 +24852,7 @@
         <v>131</v>
       </c>
       <c r="AD199" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE199" t="s" s="2">
         <v>23</v>
@@ -24866,7 +24861,7 @@
         <v>132</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>77</v>
@@ -24883,13 +24878,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24912,16 +24907,16 @@
         <v>86</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N200" t="s" s="2">
+      <c r="O200" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P200" s="2"/>
       <c r="Q200" t="s" s="2">
@@ -24971,7 +24966,7 @@
         <v>23</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>77</v>
@@ -24988,13 +24983,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25017,13 +25012,13 @@
         <v>86</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M201" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
@@ -25074,7 +25069,7 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
@@ -25091,13 +25086,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25120,13 +25115,13 @@
         <v>86</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M202" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M202" t="s" s="2">
+      <c r="N202" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
@@ -25177,7 +25172,7 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>85</v>
@@ -25194,13 +25189,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25223,13 +25218,13 @@
         <v>23</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M203" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
@@ -25280,7 +25275,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
@@ -25297,13 +25292,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25326,13 +25321,13 @@
         <v>23</v>
       </c>
       <c r="L204" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M204" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N204" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
@@ -25383,7 +25378,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25400,13 +25395,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25432,10 +25427,10 @@
         <v>128</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O205" t="s" s="2">
         <v>150</v>
@@ -25488,7 +25483,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25505,17 +25500,17 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F206" s="2"/>
       <c r="G206" t="s" s="2">
@@ -25537,10 +25532,10 @@
         <v>128</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="O206" t="s" s="2">
         <v>150</v>
@@ -25595,7 +25590,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25612,13 +25607,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25644,10 +25639,10 @@
         <v>160</v>
       </c>
       <c r="M207" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="N207" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25677,11 +25672,11 @@
         <v>109</v>
       </c>
       <c r="Z207" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AA207" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="AA207" t="s" s="2">
-        <v>825</v>
-      </c>
       <c r="AB207" t="s" s="2">
         <v>23</v>
       </c>
@@ -25698,7 +25693,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -25715,13 +25710,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25744,13 +25739,13 @@
         <v>23</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="M208" t="s" s="2">
+      <c r="N208" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -25801,7 +25796,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>85</v>
@@ -25818,13 +25813,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -25847,19 +25842,19 @@
         <v>23</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="M209" t="s" s="2">
+      <c r="N209" t="s" s="2">
         <v>832</v>
       </c>
-      <c r="N209" t="s" s="2">
+      <c r="O209" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="O209" t="s" s="2">
+      <c r="P209" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="P209" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="Q209" t="s" s="2">
         <v>23</v>
@@ -25908,7 +25903,7 @@
         <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -25925,13 +25920,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -25957,13 +25952,13 @@
         <v>160</v>
       </c>
       <c r="M210" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="N210" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="N210" t="s" s="2">
-        <v>838</v>
-      </c>
       <c r="O210" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -25989,14 +25984,14 @@
         <v>23</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="Z210" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="AA210" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="AA210" t="s" s="2">
-        <v>840</v>
-      </c>
       <c r="AB210" t="s" s="2">
         <v>23</v>
       </c>
@@ -26013,7 +26008,7 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
@@ -26030,7 +26025,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>129</v>
@@ -26062,10 +26057,10 @@
         <v>79</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" s="2"/>
@@ -26133,13 +26128,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26162,13 +26157,13 @@
         <v>23</v>
       </c>
       <c r="L212" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M212" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N212" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -26219,7 +26214,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -26236,13 +26231,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26313,7 +26308,7 @@
         <v>131</v>
       </c>
       <c r="AD213" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE213" t="s" s="2">
         <v>23</v>
@@ -26322,7 +26317,7 @@
         <v>132</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -26339,13 +26334,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26371,13 +26366,13 @@
         <v>99</v>
       </c>
       <c r="M214" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N214" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P214" s="2"/>
       <c r="Q214" t="s" s="2">
@@ -26385,7 +26380,7 @@
       </c>
       <c r="R214" s="2"/>
       <c r="S214" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="T214" t="s" s="2">
         <v>23</v>
@@ -26427,7 +26422,7 @@
         <v>23</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>85</v>
@@ -26444,13 +26439,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26476,10 +26471,10 @@
         <v>160</v>
       </c>
       <c r="M215" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N215" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
@@ -26530,7 +26525,7 @@
         <v>23</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>77</v>
@@ -26547,7 +26542,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>129</v>
@@ -26650,13 +26645,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26679,13 +26674,13 @@
         <v>23</v>
       </c>
       <c r="L217" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M217" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="N217" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M217" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
@@ -26736,7 +26731,7 @@
         <v>23</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>77</v>
@@ -26753,13 +26748,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -26830,7 +26825,7 @@
         <v>131</v>
       </c>
       <c r="AD218" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AE218" t="s" s="2">
         <v>23</v>
@@ -26839,7 +26834,7 @@
         <v>132</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>77</v>
@@ -26856,13 +26851,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -26888,13 +26883,13 @@
         <v>99</v>
       </c>
       <c r="M219" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N219" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N219" t="s" s="2">
+      <c r="O219" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O219" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P219" s="2"/>
       <c r="Q219" t="s" s="2">
@@ -26902,7 +26897,7 @@
       </c>
       <c r="R219" s="2"/>
       <c r="S219" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="T219" t="s" s="2">
         <v>23</v>
@@ -26944,7 +26939,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>85</v>
@@ -26961,13 +26956,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -26990,13 +26985,13 @@
         <v>23</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M220" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N220" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O220" s="2"/>
       <c r="P220" s="2"/>
@@ -27047,7 +27042,7 @@
         <v>23</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8430" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9465" uniqueCount="1035">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -899,7 +899,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -955,7 +955,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -972,7 +972,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1553,6 +1553,10 @@
     <t>Condition.asserter</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-relatedperson)
+</t>
+  </si>
+  <si>
     <t>Quelle der Information zur Diagnose (z. B. behandelnde GDA, Patient oder Dritter).</t>
   </si>
   <si>
@@ -1790,7 +1794,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
@@ -2035,7 +2039,7 @@
     <t>List.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|Device)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole|https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient|Device)
 </t>
   </si>
   <si>
@@ -2918,6 +2922,297 @@
   </si>
   <si>
     <t>element:AllergyIntolerance.reaction</t>
+  </si>
+  <si>
+    <t>at-elga-ediag-relatedperson</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-relatedperson</t>
+  </si>
+  <si>
+    <t>AtEdiagRelatedPerson</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Diagnose RelatedPerson</t>
+  </si>
+  <si>
+    <t>Das AT e-Diagnose RelatedPerson-Profil leitet sich vom RelatedPerson-Profil ab und passt dieses für die Anforderungen der e-Diagnose an.</t>
+  </si>
+  <si>
+    <t>RelatedPerson</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+  </si>
+  <si>
+    <t>AT e-Diagnose RelatedPerson</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.meta</t>
+  </si>
+  <si>
+    <t>RelatedPerson.implicitRules</t>
+  </si>
+  <si>
+    <t>RelatedPerson.language</t>
+  </si>
+  <si>
+    <t>RelatedPerson.text</t>
+  </si>
+  <si>
+    <t>RelatedPerson.contained</t>
+  </si>
+  <si>
+    <t>RelatedPerson.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.modifierExtension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.identifier</t>
+  </si>
+  <si>
+    <t>A human identifier for this person</t>
+  </si>
+  <si>
+    <t>Identifier for a person within a particular scope.</t>
+  </si>
+  <si>
+    <t>People are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the patient. Examples are national person identifier and local identifier.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.active</t>
+  </si>
+  <si>
+    <t>Für den jeweiligen Eintrag der e-Diagnose ist diese Bezugsperson als aktiv zu kennzeichnen.</t>
+  </si>
+  <si>
+    <t>Whether this related person record is in active use.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a related person record as not to be used, such as if it was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>RelatedPerson.patient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The patient this person is related to</t>
+  </si>
+  <si>
+    <t>The patient this person is related to.</t>
+  </si>
+  <si>
+    <t>We need to know which patient this RelatedPerson is related to.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship</t>
+  </si>
+  <si>
+    <t>The nature of the relationship</t>
+  </si>
+  <si>
+    <t>The nature of the relationship between a patient and the related person.</t>
+  </si>
+  <si>
+    <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship.text</t>
+  </si>
+  <si>
+    <t>Beziehung der Bezugsperson zum Patienten (z. B. Mutter, Vater, Ehepartner).</t>
+  </si>
+  <si>
+    <t>RelatedPerson.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName
+</t>
+  </si>
+  <si>
+    <t>Name der Bezugsperson.</t>
+  </si>
+  <si>
+    <t>A name associated with the person.</t>
+  </si>
+  <si>
+    <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>A contact detail for the person</t>
+  </si>
+  <si>
+    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
+  </si>
+  <si>
+    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
+  </si>
+  <si>
+    <t>People have (primary) ways to contact them in some way such as phone, email.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.gender</t>
+  </si>
+  <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>Needed for identification of the person, in combination with (at least) name and birth date.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+  </si>
+  <si>
+    <t>RelatedPerson.birthDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>The date on which the related person was born</t>
+  </si>
+  <si>
+    <t>The date on which the related person was born.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
+  </si>
+  <si>
+    <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Image of the person</t>
+  </si>
+  <si>
+    <t>Image of the person.</t>
+  </si>
+  <si>
+    <t>Many EHR systems have the capability to capture an image of persons. Fits with newer social media usage too.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.period</t>
+  </si>
+  <si>
+    <t>Period of time that this relationship is considered valid</t>
+  </si>
+  <si>
+    <t>The period of time during which this relationship is or was active. If there are no dates defined, then the interval is unknown.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication</t>
+  </si>
+  <si>
+    <t>A language which may be used to communicate with about the patient's health</t>
+  </si>
+  <si>
+    <t>A language which may be used to communicate with about the patient's health.</t>
+  </si>
+  <si>
+    <t>If no language is specified, this *implies* that the default local language is spoken.  If you need to convey proficiency for multiple modes, then you need multiple RelatedPerson.Communication associations.   If the RelatedPerson does not speak the default local language, then the Interpreter Required Standard can be used to explicitly declare that an interpreter is required.</t>
+  </si>
+  <si>
+    <t>If a related person does not speak the local language, interpreters may be required, so languages spoken and proficiency is an important things to keep track of both for patient and other persons of interest.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.modifierExtension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.language</t>
+  </si>
+  <si>
+    <t>The language which can be used to communicate with the patient about his or her health</t>
+  </si>
+  <si>
+    <t>The ISO-639-1 alpha 2 code in lower case for the language, optionally followed by a hyphen and the ISO-3166-1 alpha 2 code for the region in upper case; e.g. "en" for English, or "en-US" for American English versus "en-EN" for England English.</t>
+  </si>
+  <si>
+    <t>The structure aa-BB with this exact casing is one the most widely used notations for locale. However not all systems actually code this but instead have it as free text. Hence CodeableConcept instead of code as the data type.</t>
+  </si>
+  <si>
+    <t>Most systems in multilingual countries will want to convey language. Not all systems actually need the regional dialect.</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.preferred</t>
+  </si>
+  <si>
+    <t>Language preference indicator</t>
+  </si>
+  <si>
+    <t>Indicates whether or not the patient prefers this language (over other languages he masters up a certain level).</t>
+  </si>
+  <si>
+    <t>This language is specifically identified for communicating healthcare information.</t>
+  </si>
+  <si>
+    <t>People that master multiple languages up to certain level may prefer one or more, i.e. feel more confident in communicating in a particular language making other languages sort of a fall back method.</t>
   </si>
   <si>
     <t>at-elga-ediag-reported</t>
@@ -3063,7 +3358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B159"/>
+  <dimension ref="A1:B181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -3423,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="47">
@@ -3431,7 +3726,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48">
@@ -3447,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="50">
@@ -3463,7 +3758,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52">
@@ -3545,7 +3840,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="63">
@@ -3561,7 +3856,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65">
@@ -3582,26 +3877,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="70">
@@ -3617,7 +3912,7 @@
         <v>2</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="72">
@@ -3625,7 +3920,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="73">
@@ -3641,7 +3936,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="75">
@@ -3649,7 +3944,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="76">
@@ -3711,7 +4006,7 @@
         <v>24</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="84">
@@ -3747,7 +4042,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="89">
@@ -3755,7 +4050,7 @@
         <v>34</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="90">
@@ -3787,7 +4082,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="94">
@@ -3795,7 +4090,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="95">
@@ -3811,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="97">
@@ -3819,7 +4114,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="98">
@@ -3881,7 +4176,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="106">
@@ -3917,7 +4212,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="111">
@@ -3925,7 +4220,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="112">
@@ -3957,7 +4252,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="116">
@@ -3965,7 +4260,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="117">
@@ -3981,7 +4276,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="119">
@@ -3989,7 +4284,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="120">
@@ -4079,7 +4374,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="132">
@@ -4095,7 +4390,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="134">
@@ -4116,10 +4411,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="137">
@@ -4135,7 +4430,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="139">
@@ -4143,7 +4438,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="140">
@@ -4159,7 +4454,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="142">
@@ -4167,7 +4462,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>138</v>
+        <v>939</v>
       </c>
     </row>
     <row r="143">
@@ -4175,7 +4470,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>545</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144">
@@ -4229,7 +4524,7 @@
         <v>24</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>139</v>
+        <v>940</v>
       </c>
     </row>
     <row r="151">
@@ -4257,7 +4552,7 @@
         <v>30</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>546</v>
+        <v>31</v>
       </c>
     </row>
     <row r="155">
@@ -4265,7 +4560,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>129</v>
+        <v>941</v>
       </c>
     </row>
     <row r="156">
@@ -4273,7 +4568,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>547</v>
+        <v>942</v>
       </c>
     </row>
     <row r="157">
@@ -4293,11 +4588,181 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="s" s="2">
+      <c r="A159" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B159" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B166" s="2"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B174" s="2"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="B159" t="s" s="2">
-        <v>938</v>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>1034</v>
       </c>
     </row>
   </sheetData>
@@ -4307,12 +4772,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK247"/>
+  <dimension ref="A1:AK277"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.57421875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.46484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.9609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="39.671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="14.828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -14230,13 +14695,13 @@
         <v>86</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>304</v>
+        <v>492</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -14307,10 +14772,10 @@
         <v>388</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -14336,10 +14801,10 @@
         <v>318</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -14390,7 +14855,7 @@
         <v>23</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>77</v>
@@ -14402,7 +14867,7 @@
         <v>23</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="97">
@@ -14410,10 +14875,10 @@
         <v>388</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -14513,10 +14978,10 @@
         <v>388</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -14618,10 +15083,10 @@
         <v>388</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -14725,10 +15190,10 @@
         <v>388</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -14754,10 +15219,10 @@
         <v>188</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -14787,10 +15252,10 @@
         <v>337</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA100" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>23</v>
@@ -14808,7 +15273,7 @@
         <v>23</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -14817,7 +15282,7 @@
         <v>85</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>97</v>
@@ -14828,10 +15293,10 @@
         <v>388</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14854,13 +15319,13 @@
         <v>23</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -14911,7 +15376,7 @@
         <v>23</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>77</v>
@@ -14920,7 +15385,7 @@
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>97</v>
@@ -14931,10 +15396,10 @@
         <v>388</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -14960,10 +15425,10 @@
         <v>188</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -14993,10 +15458,10 @@
         <v>337</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>23</v>
@@ -15014,7 +15479,7 @@
         <v>23</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>77</v>
@@ -15034,10 +15499,10 @@
         <v>388</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -15063,13 +15528,13 @@
         <v>318</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P103" s="2"/>
       <c r="Q103" t="s" s="2">
@@ -15119,7 +15584,7 @@
         <v>23</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>77</v>
@@ -15131,7 +15596,7 @@
         <v>23</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="104">
@@ -15139,10 +15604,10 @@
         <v>388</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -15242,10 +15707,10 @@
         <v>388</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -15347,10 +15812,10 @@
         <v>388</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -15454,10 +15919,10 @@
         <v>388</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -15483,10 +15948,10 @@
         <v>188</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -15516,10 +15981,10 @@
         <v>337</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AB107" t="s" s="2">
         <v>23</v>
@@ -15537,7 +16002,7 @@
         <v>23</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -15546,7 +16011,7 @@
         <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>97</v>
@@ -15557,10 +16022,10 @@
         <v>388</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -15583,13 +16048,13 @@
         <v>86</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
@@ -15640,7 +16105,7 @@
         <v>23</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>77</v>
@@ -15649,7 +16114,7 @@
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>97</v>
@@ -15660,10 +16125,10 @@
         <v>388</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -15689,10 +16154,10 @@
         <v>313</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -15743,7 +16208,7 @@
         <v>23</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>77</v>
@@ -15763,10 +16228,10 @@
         <v>388</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15866,10 +16331,10 @@
         <v>388</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -15971,10 +16436,10 @@
         <v>388</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16076,10 +16541,10 @@
         <v>388</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -16179,10 +16644,10 @@
         <v>388</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -16279,7 +16744,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>129</v>
@@ -16382,13 +16847,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -16485,13 +16950,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -16499,7 +16964,7 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
@@ -16588,16 +17053,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E118" t="s" s="2">
         <v>23</v>
@@ -16693,13 +17158,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16796,13 +17261,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16899,13 +17364,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16931,13 +17396,13 @@
         <v>99</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
@@ -16945,7 +17410,7 @@
       </c>
       <c r="R121" s="2"/>
       <c r="S121" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>23</v>
@@ -16987,7 +17452,7 @@
         <v>23</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>85</v>
@@ -17004,13 +17469,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17033,13 +17498,13 @@
         <v>23</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -17090,7 +17555,7 @@
         <v>23</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>77</v>
@@ -17107,16 +17572,16 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E123" t="s" s="2">
         <v>23</v>
@@ -17212,13 +17677,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -17315,13 +17780,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -17418,13 +17883,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -17450,13 +17915,13 @@
         <v>99</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
@@ -17464,7 +17929,7 @@
       </c>
       <c r="R126" s="2"/>
       <c r="S126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>23</v>
@@ -17506,7 +17971,7 @@
         <v>23</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>85</v>
@@ -17523,13 +17988,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17555,10 +18020,10 @@
         <v>294</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -17609,7 +18074,7 @@
         <v>23</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>77</v>
@@ -17626,16 +18091,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E128" t="s" s="2">
         <v>23</v>
@@ -17731,13 +18196,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17834,13 +18299,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17937,13 +18402,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17969,13 +18434,13 @@
         <v>99</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
@@ -17983,7 +18448,7 @@
       </c>
       <c r="R131" s="2"/>
       <c r="S131" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>23</v>
@@ -18025,7 +18490,7 @@
         <v>23</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>85</v>
@@ -18042,13 +18507,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -18074,10 +18539,10 @@
         <v>166</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -18128,7 +18593,7 @@
         <v>23</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>77</v>
@@ -18145,13 +18610,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -18177,13 +18642,13 @@
         <v>99</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -18191,7 +18656,7 @@
       </c>
       <c r="R133" s="2"/>
       <c r="S133" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>23</v>
@@ -18233,7 +18698,7 @@
         <v>23</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>85</v>
@@ -18250,13 +18715,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -18279,13 +18744,13 @@
         <v>23</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -18336,7 +18801,7 @@
         <v>23</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>77</v>
@@ -18353,17 +18818,17 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
@@ -18385,10 +18850,10 @@
         <v>79</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -18439,7 +18904,7 @@
         <v>23</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>77</v>
@@ -18451,18 +18916,18 @@
         <v>23</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -18561,13 +19026,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18664,13 +19129,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18769,13 +19234,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18874,13 +19339,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -18979,13 +19444,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19084,13 +19549,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19119,7 +19584,7 @@
         <v>172</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>150</v>
@@ -19189,13 +19654,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -19296,13 +19761,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19328,10 +19793,10 @@
         <v>154</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -19382,7 +19847,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>77</v>
@@ -19399,13 +19864,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19431,13 +19896,13 @@
         <v>105</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P145" s="2"/>
       <c r="Q145" t="s" s="2">
@@ -19445,7 +19910,7 @@
       </c>
       <c r="R145" s="2"/>
       <c r="S145" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>23</v>
@@ -19466,10 +19931,10 @@
         <v>182</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA145" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AB145" t="s" s="2">
         <v>23</v>
@@ -19487,7 +19952,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>85</v>
@@ -19504,13 +19969,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19536,23 +20001,23 @@
         <v>105</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P146" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R146" s="2"/>
       <c r="S146" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>23</v>
@@ -19573,10 +20038,10 @@
         <v>182</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AA146" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AB146" t="s" s="2">
         <v>23</v>
@@ -19594,7 +20059,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>85</v>
@@ -19611,13 +20076,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19643,14 +20108,14 @@
         <v>166</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>23</v>
@@ -19663,7 +20128,7 @@
         <v>23</v>
       </c>
       <c r="U147" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="V147" t="s" s="2">
         <v>23</v>
@@ -19699,7 +20164,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -19716,13 +20181,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19748,16 +20213,16 @@
         <v>188</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P148" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Q148" t="s" s="2">
         <v>23</v>
@@ -19786,7 +20251,7 @@
       </c>
       <c r="Z148" s="2"/>
       <c r="AA148" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AB148" t="s" s="2">
         <v>23</v>
@@ -19804,7 +20269,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -19821,13 +20286,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19853,16 +20318,16 @@
         <v>282</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P149" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>23</v>
@@ -19911,7 +20376,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -19928,13 +20393,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19960,10 +20425,10 @@
         <v>286</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -20014,7 +20479,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -20031,13 +20496,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20063,16 +20528,16 @@
         <v>294</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P151" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -20121,7 +20586,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -20138,13 +20603,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20167,19 +20632,19 @@
         <v>86</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P152" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Q152" t="s" s="2">
         <v>23</v>
@@ -20228,7 +20693,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -20245,13 +20710,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -20277,16 +20742,16 @@
         <v>188</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="P153" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="Q153" t="s" s="2">
         <v>23</v>
@@ -20314,10 +20779,10 @@
         <v>109</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AA153" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AB153" t="s" s="2">
         <v>23</v>
@@ -20335,7 +20800,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -20352,13 +20817,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20384,10 +20849,10 @@
         <v>313</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -20438,7 +20903,7 @@
         <v>23</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>77</v>
@@ -20455,13 +20920,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -20487,13 +20952,13 @@
         <v>318</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
@@ -20543,7 +21008,7 @@
         <v>23</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>77</v>
@@ -20552,7 +21017,7 @@
         <v>78</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>97</v>
@@ -20560,13 +21025,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20663,13 +21128,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20768,13 +21233,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20875,13 +21340,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20907,16 +21372,16 @@
         <v>188</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P159" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>23</v>
@@ -20944,10 +21409,10 @@
         <v>337</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA159" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AB159" t="s" s="2">
         <v>23</v>
@@ -20965,7 +21430,7 @@
         <v>23</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>77</v>
@@ -20982,13 +21447,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21011,71 +21476,71 @@
         <v>23</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="P160" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="Q160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R160" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG160" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="M160" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="Q160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R160" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="AH160" t="s" s="2">
         <v>77</v>
       </c>
@@ -21083,7 +21548,7 @@
         <v>85</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>97</v>
@@ -21091,13 +21556,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21123,14 +21588,14 @@
         <v>294</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Q161" t="s" s="2">
         <v>23</v>
@@ -21179,7 +21644,7 @@
         <v>23</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>77</v>
@@ -21196,13 +21661,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21225,13 +21690,13 @@
         <v>23</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -21282,7 +21747,7 @@
         <v>23</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>85</v>
@@ -21299,13 +21764,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21402,13 +21867,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21507,13 +21972,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21539,13 +22004,13 @@
         <v>166</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21595,7 +22060,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -21604,7 +22069,7 @@
         <v>85</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>97</v>
@@ -21612,13 +22077,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21644,13 +22109,13 @@
         <v>99</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -21679,10 +22144,10 @@
         <v>193</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA166" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AB166" t="s" s="2">
         <v>23</v>
@@ -21700,7 +22165,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -21717,13 +22182,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21749,13 +22214,13 @@
         <v>154</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -21805,7 +22270,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -21822,13 +22287,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21854,13 +22319,13 @@
         <v>166</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -21910,7 +22375,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -21927,13 +22392,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21959,16 +22424,16 @@
         <v>188</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="P169" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="Q169" t="s" s="2">
         <v>23</v>
@@ -21997,7 +22462,7 @@
       </c>
       <c r="Z169" s="2"/>
       <c r="AA169" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AB169" t="s" s="2">
         <v>23</v>
@@ -22015,7 +22480,7 @@
         <v>23</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>77</v>
@@ -22024,7 +22489,7 @@
         <v>85</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>97</v>
@@ -22032,13 +22497,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22064,10 +22529,10 @@
         <v>79</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -22118,7 +22583,7 @@
         <v>23</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>77</v>
@@ -22130,18 +22595,18 @@
         <v>23</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -22240,13 +22705,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -22343,13 +22808,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22448,13 +22913,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22553,13 +23018,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22658,13 +23123,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22763,13 +23228,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22864,13 +23329,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B178" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C178" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>136</v>
@@ -22969,13 +23434,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>142</v>
@@ -23074,13 +23539,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23181,13 +23646,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23213,16 +23678,16 @@
         <v>154</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P181" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Q181" t="s" s="2">
         <v>23</v>
@@ -23269,7 +23734,7 @@
         <v>132</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -23286,13 +23751,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>161</v>
@@ -23326,10 +23791,10 @@
         <v>163</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P182" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Q182" t="s" s="2">
         <v>23</v>
@@ -23378,7 +23843,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -23395,13 +23860,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -23498,13 +23963,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23603,13 +24068,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -23710,13 +24175,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23817,13 +24282,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23924,13 +24389,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24029,13 +24494,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24132,13 +24597,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24237,13 +24702,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24266,13 +24731,13 @@
         <v>86</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
@@ -24323,7 +24788,7 @@
         <v>23</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>77</v>
@@ -24340,13 +24805,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24372,13 +24837,13 @@
         <v>99</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P192" s="2"/>
       <c r="Q192" t="s" s="2">
@@ -24428,7 +24893,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>77</v>
@@ -24445,17 +24910,17 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" t="s" s="2">
@@ -24474,13 +24939,13 @@
         <v>86</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -24531,7 +24996,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24548,17 +25013,17 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" t="s" s="2">
@@ -24577,16 +25042,16 @@
         <v>86</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24636,7 +25101,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -24653,13 +25118,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24685,13 +25150,13 @@
         <v>105</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P195" s="2"/>
       <c r="Q195" t="s" s="2">
@@ -24699,7 +25164,7 @@
       </c>
       <c r="R195" s="2"/>
       <c r="S195" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="T195" t="s" s="2">
         <v>23</v>
@@ -24720,10 +25185,10 @@
         <v>182</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA195" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AB195" t="s" s="2">
         <v>23</v>
@@ -24741,7 +25206,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>85</v>
@@ -24758,17 +25223,17 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F196" s="2"/>
       <c r="G196" t="s" s="2">
@@ -24790,13 +25255,13 @@
         <v>188</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P196" s="2"/>
       <c r="Q196" t="s" s="2">
@@ -24825,10 +25290,10 @@
         <v>337</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AA196" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AB196" t="s" s="2">
         <v>23</v>
@@ -24846,7 +25311,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -24863,13 +25328,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24895,10 +25360,10 @@
         <v>188</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -24928,10 +25393,10 @@
         <v>337</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AA197" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AB197" t="s" s="2">
         <v>23</v>
@@ -24949,7 +25414,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -24966,13 +25431,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24998,10 +25463,10 @@
         <v>188</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -25034,7 +25499,7 @@
       </c>
       <c r="Z198" s="2"/>
       <c r="AA198" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AB198" t="s" s="2">
         <v>23</v>
@@ -25052,7 +25517,7 @@
         <v>23</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>77</v>
@@ -25069,13 +25534,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25172,13 +25637,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -25277,13 +25742,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25384,13 +25849,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25491,13 +25956,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25523,10 +25988,10 @@
         <v>282</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
@@ -25577,7 +26042,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>85</v>
@@ -25594,13 +26059,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25629,10 +26094,10 @@
         <v>287</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
@@ -25682,7 +26147,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25699,13 +26164,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25731,13 +26196,13 @@
         <v>294</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -25787,7 +26252,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25804,13 +26269,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25836,7 +26301,7 @@
         <v>299</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N206" t="s" s="2">
         <v>301</v>
@@ -25890,7 +26355,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25907,13 +26372,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25936,13 +26401,13 @@
         <v>86</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>304</v>
+        <v>492</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25993,7 +26458,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26010,13 +26475,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -26042,10 +26507,10 @@
         <v>318</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -26096,7 +26561,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26113,13 +26578,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26216,13 +26681,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26321,13 +26786,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26428,13 +26893,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26460,14 +26925,14 @@
         <v>188</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="Q212" t="s" s="2">
         <v>23</v>
@@ -26495,10 +26960,10 @@
         <v>337</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AA212" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AB212" t="s" s="2">
         <v>23</v>
@@ -26516,7 +26981,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -26533,13 +26998,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26562,17 +27027,17 @@
         <v>86</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Q213" t="s" s="2">
         <v>23</v>
@@ -26621,7 +27086,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>85</v>
@@ -26638,13 +27103,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26670,14 +27135,14 @@
         <v>221</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="Q214" t="s" s="2">
         <v>23</v>
@@ -26726,7 +27191,7 @@
         <v>23</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>77</v>
@@ -26743,13 +27208,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26772,17 +27237,17 @@
         <v>86</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q215" t="s" s="2">
         <v>23</v>
@@ -26831,7 +27296,7 @@
         <v>23</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>77</v>
@@ -26848,13 +27313,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26880,13 +27345,13 @@
         <v>188</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="P216" s="2"/>
       <c r="Q216" t="s" s="2">
@@ -26915,10 +27380,10 @@
         <v>337</v>
       </c>
       <c r="Z216" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AA216" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AB216" t="s" s="2">
         <v>23</v>
@@ -26936,7 +27401,7 @@
         <v>23</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>77</v>
@@ -26953,13 +27418,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26982,16 +27447,16 @@
         <v>86</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="O217" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P217" s="2"/>
       <c r="Q217" t="s" s="2">
@@ -27041,7 +27506,7 @@
         <v>23</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>77</v>
@@ -27058,13 +27523,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27090,13 +27555,13 @@
         <v>188</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="P218" s="2"/>
       <c r="Q218" t="s" s="2">
@@ -27146,7 +27611,7 @@
         <v>23</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>77</v>
@@ -27163,13 +27628,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27195,13 +27660,13 @@
         <v>188</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="O219" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="P219" s="2"/>
       <c r="Q219" t="s" s="2">
@@ -27230,10 +27695,10 @@
         <v>337</v>
       </c>
       <c r="Z219" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AA219" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AB219" t="s" s="2">
         <v>23</v>
@@ -27251,7 +27716,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -27268,13 +27733,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27297,16 +27762,16 @@
         <v>23</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="P220" s="2"/>
       <c r="Q220" t="s" s="2">
@@ -27356,7 +27821,7 @@
         <v>23</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>77</v>
@@ -27373,13 +27838,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27405,13 +27870,13 @@
         <v>188</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="P221" s="2"/>
       <c r="Q221" t="s" s="2">
@@ -27440,10 +27905,10 @@
         <v>337</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="AA221" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AB221" t="s" s="2">
         <v>23</v>
@@ -27461,7 +27926,7 @@
         <v>23</v>
       </c>
       <c r="AG221" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AH221" t="s" s="2">
         <v>77</v>
@@ -27478,13 +27943,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27507,17 +27972,17 @@
         <v>23</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="Q222" t="s" s="2">
         <v>23</v>
@@ -27566,7 +28031,7 @@
         <v>23</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>77</v>
@@ -27583,13 +28048,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27615,10 +28080,10 @@
         <v>188</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27648,10 +28113,10 @@
         <v>337</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>23</v>
@@ -27669,7 +28134,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -27686,13 +28151,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27718,10 +28183,10 @@
         <v>313</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -27772,7 +28237,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>77</v>
@@ -27789,13 +28254,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27892,13 +28357,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -27997,13 +28462,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -28102,13 +28567,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28205,13 +28670,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28308,13 +28773,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28340,10 +28805,10 @@
         <v>318</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" s="2"/>
@@ -28394,7 +28859,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>77</v>
@@ -28411,13 +28876,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28514,13 +28979,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28619,13 +29084,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28726,13 +29191,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -28758,10 +29223,10 @@
         <v>188</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" s="2"/>
@@ -28791,10 +29256,10 @@
         <v>109</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AA234" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AB234" t="s" s="2">
         <v>23</v>
@@ -28812,7 +29277,7 @@
         <v>23</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>77</v>
@@ -28829,13 +29294,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28858,13 +29323,13 @@
         <v>23</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" s="2"/>
@@ -28915,7 +29380,7 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>85</v>
@@ -28932,13 +29397,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -28961,19 +29426,19 @@
         <v>23</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="P236" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="Q236" t="s" s="2">
         <v>23</v>
@@ -29022,7 +29487,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29039,13 +29504,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29071,13 +29536,13 @@
         <v>188</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
@@ -29106,10 +29571,10 @@
         <v>337</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AA237" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="AB237" t="s" s="2">
         <v>23</v>
@@ -29127,7 +29592,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>77</v>
@@ -29144,7 +29609,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>129</v>
@@ -29176,7 +29641,7 @@
         <v>79</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N238" t="s" s="2">
         <v>327</v>
@@ -29247,13 +29712,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -29350,13 +29815,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29453,13 +29918,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -29485,13 +29950,13 @@
         <v>99</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O241" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P241" s="2"/>
       <c r="Q241" t="s" s="2">
@@ -29499,7 +29964,7 @@
       </c>
       <c r="R241" s="2"/>
       <c r="S241" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>23</v>
@@ -29541,7 +30006,7 @@
         <v>23</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>85</v>
@@ -29558,13 +30023,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -29590,10 +30055,10 @@
         <v>188</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
@@ -29644,7 +30109,7 @@
         <v>23</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>77</v>
@@ -29661,13 +30126,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>129</v>
+        <v>941</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>129</v>
+        <v>941</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -29693,10 +30158,10 @@
         <v>79</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>138</v>
+        <v>943</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>139</v>
+        <v>944</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -29747,7 +30212,7 @@
         <v>23</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>129</v>
+        <v>941</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>77</v>
@@ -29756,21 +30221,21 @@
         <v>78</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>134</v>
+        <v>736</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>552</v>
+        <v>945</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>552</v>
+        <v>945</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -29790,18 +30255,20 @@
         <v>23</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>167</v>
+        <v>88</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O244" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="O244" t="s" s="2">
+        <v>90</v>
+      </c>
       <c r="P244" s="2"/>
       <c r="Q244" t="s" s="2">
         <v>23</v>
@@ -29850,7 +30317,7 @@
         <v>23</v>
       </c>
       <c r="AG244" t="s" s="2">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="AH244" t="s" s="2">
         <v>77</v>
@@ -29867,13 +30334,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>553</v>
+        <v>946</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>553</v>
+        <v>946</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -29884,7 +30351,7 @@
         <v>77</v>
       </c>
       <c r="H245" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I245" t="s" s="2">
         <v>23</v>
@@ -29893,16 +30360,16 @@
         <v>23</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="O245" s="2"/>
       <c r="P245" s="2"/>
@@ -29941,42 +30408,42 @@
         <v>23</v>
       </c>
       <c r="AC245" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD245" t="s" s="2">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="AE245" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI245" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ245" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK245" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>566</v>
+        <v>947</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>566</v>
+        <v>947</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -29984,7 +30451,7 @@
       </c>
       <c r="F246" s="2"/>
       <c r="G246" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>85</v>
@@ -29993,22 +30460,22 @@
         <v>23</v>
       </c>
       <c r="J246" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L246" t="s" s="2">
         <v>99</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>563</v>
+        <v>100</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>564</v>
+        <v>101</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>565</v>
+        <v>102</v>
       </c>
       <c r="P246" s="2"/>
       <c r="Q246" t="s" s="2">
@@ -30016,7 +30483,7 @@
       </c>
       <c r="R246" s="2"/>
       <c r="S246" t="s" s="2">
-        <v>936</v>
+        <v>23</v>
       </c>
       <c r="T246" t="s" s="2">
         <v>23</v>
@@ -30058,10 +30525,10 @@
         <v>23</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>566</v>
+        <v>103</v>
       </c>
       <c r="AH246" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI246" t="s" s="2">
         <v>85</v>
@@ -30070,18 +30537,18 @@
         <v>23</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>572</v>
+        <v>948</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>572</v>
+        <v>948</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -30104,15 +30571,17 @@
         <v>23</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>680</v>
+        <v>105</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>570</v>
+        <v>106</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O247" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O247" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P247" s="2"/>
       <c r="Q247" t="s" s="2">
         <v>23</v>
@@ -30137,13 +30606,13 @@
         <v>23</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="AA247" t="s" s="2">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="AB247" t="s" s="2">
         <v>23</v>
@@ -30161,18 +30630,3172 @@
         <v>23</v>
       </c>
       <c r="AG247" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="C248" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="D248" s="2"/>
+      <c r="E248" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="F248" s="2"/>
+      <c r="G248" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O248" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="P248" s="2"/>
+      <c r="Q248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R248" s="2"/>
+      <c r="S248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK248" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="C249" t="s" s="2">
+        <v>950</v>
+      </c>
+      <c r="D249" s="2"/>
+      <c r="E249" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F249" s="2"/>
+      <c r="G249" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H249" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L249" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M249" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N249" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="P249" s="2"/>
+      <c r="Q249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R249" s="2"/>
+      <c r="S249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG249" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AH249" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI249" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK249" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="C250" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="D250" s="2"/>
+      <c r="E250" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F250" s="2"/>
+      <c r="G250" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L250" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M250" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N250" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O250" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P250" s="2"/>
+      <c r="Q250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R250" s="2"/>
+      <c r="S250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK250" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="C251" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="D251" s="2"/>
+      <c r="E251" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F251" s="2"/>
+      <c r="G251" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J251" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L251" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M251" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N251" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O251" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P251" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Q251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R251" s="2"/>
+      <c r="S251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG251" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AH251" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI251" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK251" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="C252" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="D252" s="2"/>
+      <c r="E252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F252" s="2"/>
+      <c r="G252" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H252" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K252" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L252" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M252" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="N252" t="s" s="2">
+        <v>955</v>
+      </c>
+      <c r="O252" s="2"/>
+      <c r="P252" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="Q252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R252" s="2"/>
+      <c r="S252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG252" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="AH252" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI252" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK252" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="C253" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="D253" s="2"/>
+      <c r="E253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F253" s="2"/>
+      <c r="G253" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H253" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I253" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J253" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K253" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L253" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M253" t="s" s="2">
+        <v>958</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="O253" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="P253" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="Q253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R253" t="s" s="2">
+        <v>962</v>
+      </c>
+      <c r="S253" t="s" s="2">
+        <v>963</v>
+      </c>
+      <c r="T253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG253" t="s" s="2">
+        <v>957</v>
+      </c>
+      <c r="AH253" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI253" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK253" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="C254" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="D254" s="2"/>
+      <c r="E254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F254" s="2"/>
+      <c r="G254" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H254" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K254" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L254" t="s" s="2">
+        <v>965</v>
+      </c>
+      <c r="M254" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="N254" t="s" s="2">
+        <v>967</v>
+      </c>
+      <c r="O254" s="2"/>
+      <c r="P254" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="Q254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R254" s="2"/>
+      <c r="S254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG254" t="s" s="2">
+        <v>964</v>
+      </c>
+      <c r="AH254" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI254" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ254" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK254" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="C255" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="D255" s="2"/>
+      <c r="E255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F255" s="2"/>
+      <c r="G255" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H255" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I255" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K255" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L255" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M255" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="O255" s="2"/>
+      <c r="P255" t="s" s="2">
+        <v>972</v>
+      </c>
+      <c r="Q255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R255" s="2"/>
+      <c r="S255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y255" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z255" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="AA255" t="s" s="2">
+        <v>973</v>
+      </c>
+      <c r="AB255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG255" t="s" s="2">
+        <v>969</v>
+      </c>
+      <c r="AH255" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI255" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK255" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="D256" s="2"/>
+      <c r="E256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F256" s="2"/>
+      <c r="G256" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H256" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L256" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M256" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N256" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O256" s="2"/>
+      <c r="P256" s="2"/>
+      <c r="Q256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R256" s="2"/>
+      <c r="S256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG256" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AH256" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI256" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ256" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK256" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="D257" s="2"/>
+      <c r="E257" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F257" s="2"/>
+      <c r="G257" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H257" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L257" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M257" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N257" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O257" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P257" s="2"/>
+      <c r="Q257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R257" s="2"/>
+      <c r="S257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC257" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AD257" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AE257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF257" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG257" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AH257" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI257" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ257" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK257" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="C258" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="D258" s="2"/>
+      <c r="E258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F258" s="2"/>
+      <c r="G258" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H258" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K258" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L258" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M258" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N258" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O258" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="P258" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Q258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R258" s="2"/>
+      <c r="S258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG258" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AH258" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI258" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ258" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK258" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="C259" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="D259" s="2"/>
+      <c r="E259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F259" s="2"/>
+      <c r="G259" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H259" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K259" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L259" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M259" t="s" s="2">
+        <v>978</v>
+      </c>
+      <c r="N259" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O259" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P259" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="Q259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R259" s="2"/>
+      <c r="S259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG259" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AH259" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI259" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK259" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="C260" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="D260" s="2"/>
+      <c r="E260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F260" s="2"/>
+      <c r="G260" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H260" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I260" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K260" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L260" t="s" s="2">
+        <v>980</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="N260" t="s" s="2">
+        <v>982</v>
+      </c>
+      <c r="O260" s="2"/>
+      <c r="P260" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="Q260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R260" s="2"/>
+      <c r="S260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG260" t="s" s="2">
+        <v>979</v>
+      </c>
+      <c r="AH260" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI260" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ260" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK260" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="C261" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="D261" s="2"/>
+      <c r="E261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F261" s="2"/>
+      <c r="G261" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H261" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K261" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L261" t="s" s="2">
+        <v>985</v>
+      </c>
+      <c r="M261" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="O261" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="P261" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="Q261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R261" s="2"/>
+      <c r="S261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG261" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="AH261" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI261" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ261" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK261" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="C262" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="D262" s="2"/>
+      <c r="E262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F262" s="2"/>
+      <c r="G262" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H262" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K262" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L262" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M262" t="s" s="2">
+        <v>991</v>
+      </c>
+      <c r="N262" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="O262" s="2"/>
+      <c r="P262" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="Q262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R262" s="2"/>
+      <c r="S262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y262" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z262" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="AA262" t="s" s="2">
+        <v>995</v>
+      </c>
+      <c r="AB262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG262" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="AH262" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI262" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ262" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK262" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="D263" s="2"/>
+      <c r="E263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F263" s="2"/>
+      <c r="G263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L263" t="s" s="2">
+        <v>997</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="N263" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="O263" s="2"/>
+      <c r="P263" s="2"/>
+      <c r="Q263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R263" s="2"/>
+      <c r="S263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG263" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="AH263" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI263" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ263" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK263" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C264" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D264" s="2"/>
+      <c r="E264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F264" s="2"/>
+      <c r="G264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K264" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L264" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="M264" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="N264" t="s" s="2">
+        <v>1003</v>
+      </c>
+      <c r="O264" s="2"/>
+      <c r="P264" t="s" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R264" s="2"/>
+      <c r="S264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG264" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="AH264" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI264" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ264" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK264" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C265" t="s" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D265" s="2"/>
+      <c r="E265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F265" s="2"/>
+      <c r="G265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L265" t="s" s="2">
+        <v>1006</v>
+      </c>
+      <c r="M265" t="s" s="2">
+        <v>1007</v>
+      </c>
+      <c r="N265" t="s" s="2">
+        <v>1008</v>
+      </c>
+      <c r="O265" s="2"/>
+      <c r="P265" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="Q265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R265" s="2"/>
+      <c r="S265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG265" t="s" s="2">
+        <v>1005</v>
+      </c>
+      <c r="AH265" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI265" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ265" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK265" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C266" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="D266" s="2"/>
+      <c r="E266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F266" s="2"/>
+      <c r="G266" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L266" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M266" t="s" s="2">
+        <v>1011</v>
+      </c>
+      <c r="N266" t="s" s="2">
+        <v>1012</v>
+      </c>
+      <c r="O266" s="2"/>
+      <c r="P266" s="2"/>
+      <c r="Q266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R266" s="2"/>
+      <c r="S266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG266" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="AH266" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI266" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ266" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK266" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C267" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="D267" s="2"/>
+      <c r="E267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F267" s="2"/>
+      <c r="G267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L267" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M267" t="s" s="2">
+        <v>1014</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="O267" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="P267" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="Q267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R267" s="2"/>
+      <c r="S267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG267" t="s" s="2">
+        <v>1013</v>
+      </c>
+      <c r="AH267" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI267" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ267" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK267" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C268" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="D268" s="2"/>
+      <c r="E268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F268" s="2"/>
+      <c r="G268" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H268" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L268" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M268" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N268" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O268" s="2"/>
+      <c r="P268" s="2"/>
+      <c r="Q268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R268" s="2"/>
+      <c r="S268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG268" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AH268" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI268" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ268" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK268" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="C269" t="s" s="2">
+        <v>1019</v>
+      </c>
+      <c r="D269" s="2"/>
+      <c r="E269" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F269" s="2"/>
+      <c r="G269" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L269" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M269" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N269" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="O269" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P269" s="2"/>
+      <c r="Q269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R269" s="2"/>
+      <c r="S269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG269" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AH269" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI269" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ269" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK269" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="C270" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="D270" s="2"/>
+      <c r="E270" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="F270" s="2"/>
+      <c r="G270" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J270" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K270" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L270" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M270" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N270" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P270" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Q270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R270" s="2"/>
+      <c r="S270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG270" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AH270" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI270" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ270" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK270" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="C271" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="D271" s="2"/>
+      <c r="E271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F271" s="2"/>
+      <c r="G271" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L271" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M271" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="N271" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="O271" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="P271" t="s" s="2">
+        <v>1025</v>
+      </c>
+      <c r="Q271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R271" s="2"/>
+      <c r="S271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y271" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z271" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA271" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AB271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG271" t="s" s="2">
+        <v>1021</v>
+      </c>
+      <c r="AH271" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI271" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ271" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK271" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>936</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>1026</v>
+      </c>
+      <c r="C272" t="s" s="2">
+        <v>1026</v>
+      </c>
+      <c r="D272" s="2"/>
+      <c r="E272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F272" s="2"/>
+      <c r="G272" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H272" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L272" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M272" t="s" s="2">
+        <v>1027</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="O272" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="P272" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="Q272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R272" s="2"/>
+      <c r="S272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG272" t="s" s="2">
+        <v>1026</v>
+      </c>
+      <c r="AH272" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI272" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ272" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK272" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C273" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D273" s="2"/>
+      <c r="E273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F273" s="2"/>
+      <c r="G273" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L273" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M273" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="N273" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O273" s="2"/>
+      <c r="P273" s="2"/>
+      <c r="Q273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R273" s="2"/>
+      <c r="S273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF273" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG273" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH273" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI273" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ273" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK273" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C274" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="D274" s="2"/>
+      <c r="E274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F274" s="2"/>
+      <c r="G274" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H274" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L274" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M274" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N274" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O274" s="2"/>
+      <c r="P274" s="2"/>
+      <c r="Q274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R274" s="2"/>
+      <c r="S274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG274" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AH274" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI274" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ274" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK274" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C275" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="D275" s="2"/>
+      <c r="E275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F275" s="2"/>
+      <c r="G275" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H275" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L275" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M275" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N275" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O275" s="2"/>
+      <c r="P275" s="2"/>
+      <c r="Q275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R275" s="2"/>
+      <c r="S275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC275" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AD275" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AE275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF275" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG275" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AH275" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI275" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK275" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C276" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="D276" s="2"/>
+      <c r="E276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F276" s="2"/>
+      <c r="G276" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H276" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L276" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M276" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N276" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O276" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P276" s="2"/>
+      <c r="Q276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R276" s="2"/>
+      <c r="S276" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="T276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG276" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AH276" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI276" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ276" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK276" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C277" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="D277" s="2"/>
+      <c r="E277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F277" s="2"/>
+      <c r="G277" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H277" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L277" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="M277" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N277" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AH247" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK247" t="s" s="2">
+      <c r="O277" s="2"/>
+      <c r="P277" s="2"/>
+      <c r="Q277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R277" s="2"/>
+      <c r="S277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG277" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AH277" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI277" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK277" t="s" s="2">
         <v>97</v>
       </c>
     </row>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10130" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10130" uniqueCount="1084">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1670,11 +1670,8 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.Minimal.DocumentReference)
 </t>
-  </si>
-  <si>
-    <t>Supporting information found elsewhere</t>
   </si>
   <si>
     <t>Links to other relevant information, including pathology reports.</t>
@@ -2735,10 +2732,6 @@
   </si>
   <si>
     <t>Procedure.report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
-</t>
   </si>
   <si>
     <t>This could be a histology result, pathology report, surgical report, etc.</t>
@@ -3873,7 +3866,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="47">
@@ -3881,7 +3874,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="48">
@@ -3897,7 +3890,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="50">
@@ -3913,7 +3906,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="52">
@@ -3995,7 +3988,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="63">
@@ -4011,7 +4004,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="65">
@@ -4032,26 +4025,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>547</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="70">
@@ -4067,7 +4060,7 @@
         <v>2</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="72">
@@ -4075,7 +4068,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="73">
@@ -4091,7 +4084,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="75">
@@ -4099,7 +4092,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="76">
@@ -4161,7 +4154,7 @@
         <v>24</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="84">
@@ -4197,7 +4190,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="89">
@@ -4205,7 +4198,7 @@
         <v>34</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="90">
@@ -4237,7 +4230,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="94">
@@ -4245,7 +4238,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="95">
@@ -4261,7 +4254,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="97">
@@ -4269,7 +4262,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="98">
@@ -4331,7 +4324,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="106">
@@ -4367,7 +4360,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="111">
@@ -4375,7 +4368,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="112">
@@ -4407,7 +4400,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="116">
@@ -4415,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="117">
@@ -4431,7 +4424,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="119">
@@ -4439,7 +4432,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="120">
@@ -4529,7 +4522,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="132">
@@ -4545,7 +4538,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="134">
@@ -4566,10 +4559,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="137">
@@ -4585,7 +4578,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="139">
@@ -4593,7 +4586,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="140">
@@ -4609,7 +4602,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="142">
@@ -4617,7 +4610,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="143">
@@ -4679,7 +4672,7 @@
         <v>24</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="151">
@@ -4715,7 +4708,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="156">
@@ -4723,7 +4716,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="157">
@@ -4755,7 +4748,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="161">
@@ -4763,7 +4756,7 @@
         <v>4</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="162">
@@ -4779,7 +4772,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="164">
@@ -4795,7 +4788,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="166">
@@ -4877,7 +4870,7 @@
         <v>30</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="177">
@@ -4893,7 +4886,7 @@
         <v>34</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="179">
@@ -4914,10 +4907,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="182">
@@ -4933,7 +4926,7 @@
         <v>2</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="184">
@@ -4941,7 +4934,7 @@
         <v>4</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="185">
@@ -4957,7 +4950,7 @@
         <v>8</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="187">
@@ -4965,7 +4958,7 @@
         <v>10</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="188">
@@ -5027,7 +5020,7 @@
         <v>24</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="196">
@@ -5063,7 +5056,7 @@
         <v>32</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="201">
@@ -5071,7 +5064,7 @@
         <v>34</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="202">
@@ -16368,10 +16361,10 @@
         <v>529</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
@@ -16442,10 +16435,10 @@
         <v>387</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -16471,10 +16464,10 @@
         <v>312</v>
       </c>
       <c r="M109" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -16525,7 +16518,7 @@
         <v>23</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>77</v>
@@ -16545,10 +16538,10 @@
         <v>387</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -16648,10 +16641,10 @@
         <v>387</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16753,10 +16746,10 @@
         <v>387</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16858,10 +16851,10 @@
         <v>387</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -16961,10 +16954,10 @@
         <v>387</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -17061,7 +17054,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>129</v>
@@ -17164,13 +17157,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -17267,13 +17260,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -17281,7 +17274,7 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
@@ -17370,16 +17363,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B118" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D118" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="D118" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="E118" t="s" s="2">
         <v>23</v>
@@ -17475,13 +17468,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B119" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -17578,13 +17571,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B120" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C120" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -17681,13 +17674,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B121" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -17713,13 +17706,13 @@
         <v>99</v>
       </c>
       <c r="M121" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
@@ -17727,7 +17720,7 @@
       </c>
       <c r="R121" s="2"/>
       <c r="S121" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>23</v>
@@ -17769,7 +17762,7 @@
         <v>23</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>85</v>
@@ -17786,13 +17779,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B122" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17815,13 +17808,13 @@
         <v>23</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -17872,7 +17865,7 @@
         <v>23</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>77</v>
@@ -17889,16 +17882,16 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B123" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D123" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="D123" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="E123" t="s" s="2">
         <v>23</v>
@@ -17994,13 +17987,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -18097,13 +18090,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -18200,13 +18193,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -18232,13 +18225,13 @@
         <v>99</v>
       </c>
       <c r="M126" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N126" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P126" s="2"/>
       <c r="Q126" t="s" s="2">
@@ -18246,7 +18239,7 @@
       </c>
       <c r="R126" s="2"/>
       <c r="S126" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>23</v>
@@ -18288,7 +18281,7 @@
         <v>23</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>85</v>
@@ -18305,13 +18298,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -18337,10 +18330,10 @@
         <v>293</v>
       </c>
       <c r="M127" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -18391,7 +18384,7 @@
         <v>23</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>77</v>
@@ -18408,16 +18401,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B128" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="D128" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="D128" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="E128" t="s" s="2">
         <v>23</v>
@@ -18513,13 +18506,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -18616,13 +18609,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -18719,13 +18712,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18751,13 +18744,13 @@
         <v>99</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
@@ -18765,7 +18758,7 @@
       </c>
       <c r="R131" s="2"/>
       <c r="S131" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>23</v>
@@ -18807,7 +18800,7 @@
         <v>23</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>85</v>
@@ -18824,13 +18817,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -18856,10 +18849,10 @@
         <v>166</v>
       </c>
       <c r="M132" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -18910,7 +18903,7 @@
         <v>23</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>77</v>
@@ -18927,13 +18920,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -18959,13 +18952,13 @@
         <v>99</v>
       </c>
       <c r="M133" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P133" s="2"/>
       <c r="Q133" t="s" s="2">
@@ -18973,7 +18966,7 @@
       </c>
       <c r="R133" s="2"/>
       <c r="S133" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>23</v>
@@ -19015,7 +19008,7 @@
         <v>23</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>85</v>
@@ -19032,13 +19025,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -19061,13 +19054,13 @@
         <v>23</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M134" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -19118,7 +19111,7 @@
         <v>23</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>77</v>
@@ -19135,17 +19128,17 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
@@ -19167,10 +19160,10 @@
         <v>79</v>
       </c>
       <c r="M135" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -19221,7 +19214,7 @@
         <v>23</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>77</v>
@@ -19233,18 +19226,18 @@
         <v>23</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -19343,13 +19336,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -19446,13 +19439,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -19551,13 +19544,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -19656,13 +19649,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19761,13 +19754,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19866,13 +19859,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19901,7 +19894,7 @@
         <v>172</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>150</v>
@@ -19971,13 +19964,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -20078,13 +20071,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -20110,10 +20103,10 @@
         <v>154</v>
       </c>
       <c r="M144" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -20164,7 +20157,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>77</v>
@@ -20181,13 +20174,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -20213,13 +20206,13 @@
         <v>105</v>
       </c>
       <c r="M145" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P145" s="2"/>
       <c r="Q145" t="s" s="2">
@@ -20227,7 +20220,7 @@
       </c>
       <c r="R145" s="2"/>
       <c r="S145" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>23</v>
@@ -20248,11 +20241,11 @@
         <v>182</v>
       </c>
       <c r="Z145" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AA145" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AA145" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="AB145" t="s" s="2">
         <v>23</v>
       </c>
@@ -20269,7 +20262,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>85</v>
@@ -20286,13 +20279,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -20318,23 +20311,23 @@
         <v>105</v>
       </c>
       <c r="M146" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="O146" t="s" s="2">
+      <c r="P146" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="P146" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R146" s="2"/>
       <c r="S146" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>23</v>
@@ -20355,11 +20348,11 @@
         <v>182</v>
       </c>
       <c r="Z146" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AA146" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AA146" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="AB146" t="s" s="2">
         <v>23</v>
       </c>
@@ -20376,7 +20369,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>85</v>
@@ -20393,13 +20386,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -20425,14 +20418,14 @@
         <v>166</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>23</v>
@@ -20445,7 +20438,7 @@
         <v>23</v>
       </c>
       <c r="U147" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="V147" t="s" s="2">
         <v>23</v>
@@ -20481,7 +20474,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -20498,13 +20491,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -20530,16 +20523,16 @@
         <v>188</v>
       </c>
       <c r="M148" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="O148" t="s" s="2">
+      <c r="P148" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="Q148" t="s" s="2">
         <v>23</v>
@@ -20568,7 +20561,7 @@
       </c>
       <c r="Z148" s="2"/>
       <c r="AA148" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AB148" t="s" s="2">
         <v>23</v>
@@ -20586,7 +20579,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -20603,13 +20596,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -20635,16 +20628,16 @@
         <v>281</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="O149" t="s" s="2">
+      <c r="P149" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>23</v>
@@ -20693,7 +20686,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -20710,13 +20703,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20742,10 +20735,10 @@
         <v>285</v>
       </c>
       <c r="M150" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -20796,7 +20789,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -20813,13 +20806,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20845,16 +20838,16 @@
         <v>293</v>
       </c>
       <c r="M151" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="O151" t="s" s="2">
+      <c r="P151" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -20903,7 +20896,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -20920,13 +20913,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20949,19 +20942,19 @@
         <v>86</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="N152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="O152" t="s" s="2">
+      <c r="P152" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="Q152" t="s" s="2">
         <v>23</v>
@@ -21010,7 +21003,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -21027,13 +21020,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -21059,16 +21052,16 @@
         <v>188</v>
       </c>
       <c r="M153" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="O153" t="s" s="2">
+      <c r="P153" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="Q153" t="s" s="2">
         <v>23</v>
@@ -21096,11 +21089,11 @@
         <v>109</v>
       </c>
       <c r="Z153" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AA153" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AA153" t="s" s="2">
-        <v>658</v>
-      </c>
       <c r="AB153" t="s" s="2">
         <v>23</v>
       </c>
@@ -21117,7 +21110,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -21134,13 +21127,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -21166,10 +21159,10 @@
         <v>312</v>
       </c>
       <c r="M154" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -21220,7 +21213,7 @@
         <v>23</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>77</v>
@@ -21237,13 +21230,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -21269,13 +21262,13 @@
         <v>317</v>
       </c>
       <c r="M155" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
@@ -21325,7 +21318,7 @@
         <v>23</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>77</v>
@@ -21334,7 +21327,7 @@
         <v>78</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>97</v>
@@ -21342,13 +21335,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -21445,13 +21438,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -21550,13 +21543,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -21657,13 +21650,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21689,16 +21682,16 @@
         <v>188</v>
       </c>
       <c r="M159" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="N159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="O159" t="s" s="2">
+      <c r="P159" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="P159" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>23</v>
@@ -21726,11 +21719,11 @@
         <v>336</v>
       </c>
       <c r="Z159" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AA159" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="AA159" t="s" s="2">
-        <v>676</v>
-      </c>
       <c r="AB159" t="s" s="2">
         <v>23</v>
       </c>
@@ -21747,7 +21740,7 @@
         <v>23</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>77</v>
@@ -21764,13 +21757,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21793,79 +21786,79 @@
         <v>23</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="N160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="O160" t="s" s="2">
+      <c r="P160" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="P160" t="s" s="2">
+      <c r="Q160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R160" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="Q160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R160" t="s" s="2">
+      <c r="S160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>97</v>
@@ -21873,13 +21866,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21905,14 +21898,14 @@
         <v>293</v>
       </c>
       <c r="M161" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q161" t="s" s="2">
         <v>23</v>
@@ -21961,7 +21954,7 @@
         <v>23</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>77</v>
@@ -21978,13 +21971,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -22007,13 +22000,13 @@
         <v>23</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -22064,7 +22057,7 @@
         <v>23</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>85</v>
@@ -22081,13 +22074,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -22184,13 +22177,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -22289,13 +22282,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -22321,13 +22314,13 @@
         <v>166</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>696</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -22377,16 +22370,16 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AH165" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI165" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ165" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>97</v>
@@ -22394,13 +22387,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -22426,13 +22419,13 @@
         <v>99</v>
       </c>
       <c r="M166" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -22461,28 +22454,28 @@
         <v>193</v>
       </c>
       <c r="Z166" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AA166" t="s" s="2">
         <v>705</v>
       </c>
-      <c r="AA166" t="s" s="2">
+      <c r="AB166" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG166" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -22499,13 +22492,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -22531,13 +22524,13 @@
         <v>154</v>
       </c>
       <c r="M167" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -22587,7 +22580,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -22604,13 +22597,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -22636,13 +22629,13 @@
         <v>166</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="N168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
@@ -22692,7 +22685,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -22709,13 +22702,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22741,16 +22734,16 @@
         <v>188</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="O169" t="s" s="2">
+      <c r="P169" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="P169" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="Q169" t="s" s="2">
         <v>23</v>
@@ -22779,7 +22772,7 @@
       </c>
       <c r="Z169" s="2"/>
       <c r="AA169" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AB169" t="s" s="2">
         <v>23</v>
@@ -22797,7 +22790,7 @@
         <v>23</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>77</v>
@@ -22806,7 +22799,7 @@
         <v>85</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>97</v>
@@ -22814,13 +22807,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22846,10 +22839,10 @@
         <v>79</v>
       </c>
       <c r="M170" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -22900,7 +22893,7 @@
         <v>23</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>77</v>
@@ -22912,18 +22905,18 @@
         <v>23</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -23022,13 +23015,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -23125,13 +23118,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -23230,13 +23223,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -23335,13 +23328,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -23440,13 +23433,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -23545,13 +23538,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -23646,13 +23639,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D178" t="s" s="2">
         <v>136</v>
@@ -23751,13 +23744,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>142</v>
@@ -23856,13 +23849,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23963,13 +23956,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23995,16 +23988,16 @@
         <v>154</v>
       </c>
       <c r="M181" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N181" t="s" s="2">
         <v>745</v>
       </c>
-      <c r="N181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="O181" t="s" s="2">
+      <c r="P181" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="P181" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="Q181" t="s" s="2">
         <v>23</v>
@@ -24051,7 +24044,7 @@
         <v>132</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -24068,13 +24061,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>161</v>
@@ -24108,10 +24101,10 @@
         <v>163</v>
       </c>
       <c r="O182" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="P182" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="P182" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="Q182" t="s" s="2">
         <v>23</v>
@@ -24160,7 +24153,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -24177,13 +24170,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B183" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C183" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -24280,13 +24273,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B184" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C184" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -24385,13 +24378,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B185" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C185" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="C185" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -24492,13 +24485,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B186" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C186" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="C186" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -24599,13 +24592,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B187" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C187" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -24706,13 +24699,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B188" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C188" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24811,13 +24804,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B189" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24914,13 +24907,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B190" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C190" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -25019,13 +25012,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -25048,13 +25041,13 @@
         <v>86</v>
       </c>
       <c r="L191" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M191" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="M191" t="s" s="2">
+      <c r="N191" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
@@ -25105,7 +25098,7 @@
         <v>23</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>77</v>
@@ -25122,13 +25115,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -25154,13 +25147,13 @@
         <v>99</v>
       </c>
       <c r="M192" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="N192" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="N192" t="s" s="2">
+      <c r="O192" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="P192" s="2"/>
       <c r="Q192" t="s" s="2">
@@ -25210,7 +25203,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>77</v>
@@ -25227,17 +25220,17 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" t="s" s="2">
@@ -25256,13 +25249,13 @@
         <v>86</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
@@ -25313,7 +25306,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -25330,17 +25323,17 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" t="s" s="2">
@@ -25359,16 +25352,16 @@
         <v>86</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -25418,7 +25411,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -25435,13 +25428,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -25467,13 +25460,13 @@
         <v>105</v>
       </c>
       <c r="M195" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="N195" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="N195" t="s" s="2">
+      <c r="O195" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="P195" s="2"/>
       <c r="Q195" t="s" s="2">
@@ -25481,7 +25474,7 @@
       </c>
       <c r="R195" s="2"/>
       <c r="S195" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T195" t="s" s="2">
         <v>23</v>
@@ -25502,11 +25495,11 @@
         <v>182</v>
       </c>
       <c r="Z195" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AA195" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="AA195" t="s" s="2">
-        <v>791</v>
-      </c>
       <c r="AB195" t="s" s="2">
         <v>23</v>
       </c>
@@ -25523,7 +25516,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>85</v>
@@ -25540,17 +25533,17 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F196" s="2"/>
       <c r="G196" t="s" s="2">
@@ -25572,13 +25565,13 @@
         <v>188</v>
       </c>
       <c r="M196" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="N196" t="s" s="2">
         <v>794</v>
       </c>
-      <c r="N196" t="s" s="2">
+      <c r="O196" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="P196" s="2"/>
       <c r="Q196" t="s" s="2">
@@ -25607,11 +25600,11 @@
         <v>336</v>
       </c>
       <c r="Z196" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AA196" t="s" s="2">
         <v>797</v>
       </c>
-      <c r="AA196" t="s" s="2">
-        <v>798</v>
-      </c>
       <c r="AB196" t="s" s="2">
         <v>23</v>
       </c>
@@ -25628,7 +25621,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -25645,13 +25638,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -25677,10 +25670,10 @@
         <v>188</v>
       </c>
       <c r="M197" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N197" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -25710,11 +25703,11 @@
         <v>336</v>
       </c>
       <c r="Z197" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AA197" t="s" s="2">
         <v>802</v>
       </c>
-      <c r="AA197" t="s" s="2">
-        <v>803</v>
-      </c>
       <c r="AB197" t="s" s="2">
         <v>23</v>
       </c>
@@ -25731,7 +25724,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -25748,13 +25741,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -25780,10 +25773,10 @@
         <v>188</v>
       </c>
       <c r="M198" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="N198" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -25816,7 +25809,7 @@
       </c>
       <c r="Z198" s="2"/>
       <c r="AA198" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AB198" t="s" s="2">
         <v>23</v>
@@ -25834,7 +25827,7 @@
         <v>23</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>77</v>
@@ -25851,13 +25844,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25954,13 +25947,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -26059,13 +26052,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -26166,13 +26159,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -26273,13 +26266,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -26305,10 +26298,10 @@
         <v>281</v>
       </c>
       <c r="M203" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>813</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>814</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
@@ -26359,7 +26352,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>85</v>
@@ -26376,13 +26369,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -26411,10 +26404,10 @@
         <v>286</v>
       </c>
       <c r="N204" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="O204" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
@@ -26464,7 +26457,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -26481,13 +26474,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -26513,13 +26506,13 @@
         <v>293</v>
       </c>
       <c r="M205" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="N205" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="N205" t="s" s="2">
+      <c r="O205" t="s" s="2">
         <v>820</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -26569,7 +26562,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -26586,13 +26579,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -26618,7 +26611,7 @@
         <v>298</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="N206" t="s" s="2">
         <v>300</v>
@@ -26672,7 +26665,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -26689,13 +26682,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -26721,10 +26714,10 @@
         <v>489</v>
       </c>
       <c r="M207" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="N207" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -26775,7 +26768,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26792,13 +26785,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -26824,10 +26817,10 @@
         <v>317</v>
       </c>
       <c r="M208" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="N208" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -26878,7 +26871,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26895,13 +26888,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26998,13 +26991,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -27103,13 +27096,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -27210,13 +27203,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -27242,14 +27235,14 @@
         <v>188</v>
       </c>
       <c r="M212" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="N212" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="Q212" t="s" s="2">
         <v>23</v>
@@ -27277,11 +27270,11 @@
         <v>336</v>
       </c>
       <c r="Z212" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="AA212" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="AA212" t="s" s="2">
-        <v>838</v>
-      </c>
       <c r="AB212" t="s" s="2">
         <v>23</v>
       </c>
@@ -27298,7 +27291,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -27315,13 +27308,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -27344,17 +27337,17 @@
         <v>86</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M213" t="s" s="2">
+      <c r="N213" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Q213" t="s" s="2">
         <v>23</v>
@@ -27403,7 +27396,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>85</v>
@@ -27420,13 +27413,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -27452,14 +27445,14 @@
         <v>221</v>
       </c>
       <c r="M214" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="N214" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="Q214" t="s" s="2">
         <v>23</v>
@@ -27508,7 +27501,7 @@
         <v>23</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>77</v>
@@ -27525,13 +27518,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -27554,17 +27547,17 @@
         <v>86</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>849</v>
       </c>
-      <c r="M215" t="s" s="2">
+      <c r="N215" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="Q215" t="s" s="2">
         <v>23</v>
@@ -27613,7 +27606,7 @@
         <v>23</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>77</v>
@@ -27630,13 +27623,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -27662,13 +27655,13 @@
         <v>188</v>
       </c>
       <c r="M216" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="N216" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="N216" t="s" s="2">
+      <c r="O216" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="P216" s="2"/>
       <c r="Q216" t="s" s="2">
@@ -27697,11 +27690,11 @@
         <v>336</v>
       </c>
       <c r="Z216" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="AA216" t="s" s="2">
         <v>857</v>
       </c>
-      <c r="AA216" t="s" s="2">
-        <v>858</v>
-      </c>
       <c r="AB216" t="s" s="2">
         <v>23</v>
       </c>
@@ -27718,7 +27711,7 @@
         <v>23</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>77</v>
@@ -27735,13 +27728,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -27764,16 +27757,16 @@
         <v>86</v>
       </c>
       <c r="L217" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="M217" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="M217" t="s" s="2">
+      <c r="N217" t="s" s="2">
         <v>861</v>
       </c>
-      <c r="N217" t="s" s="2">
+      <c r="O217" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="P217" s="2"/>
       <c r="Q217" t="s" s="2">
@@ -27823,7 +27816,7 @@
         <v>23</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>77</v>
@@ -27840,13 +27833,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27872,13 +27865,13 @@
         <v>188</v>
       </c>
       <c r="M218" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="N218" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="N218" t="s" s="2">
+      <c r="O218" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="P218" s="2"/>
       <c r="Q218" t="s" s="2">
@@ -27928,7 +27921,7 @@
         <v>23</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>77</v>
@@ -27945,13 +27938,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27977,13 +27970,13 @@
         <v>188</v>
       </c>
       <c r="M219" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="N219" t="s" s="2">
         <v>869</v>
       </c>
-      <c r="N219" t="s" s="2">
+      <c r="O219" t="s" s="2">
         <v>870</v>
-      </c>
-      <c r="O219" t="s" s="2">
-        <v>871</v>
       </c>
       <c r="P219" s="2"/>
       <c r="Q219" t="s" s="2">
@@ -28012,11 +28005,11 @@
         <v>336</v>
       </c>
       <c r="Z219" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="AA219" t="s" s="2">
         <v>872</v>
       </c>
-      <c r="AA219" t="s" s="2">
-        <v>873</v>
-      </c>
       <c r="AB219" t="s" s="2">
         <v>23</v>
       </c>
@@ -28033,7 +28026,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -28050,13 +28043,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -28079,16 +28072,16 @@
         <v>23</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>875</v>
+        <v>529</v>
       </c>
       <c r="M220" t="s" s="2">
         <v>515</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="O220" t="s" s="2">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="P220" s="2"/>
       <c r="Q220" t="s" s="2">
@@ -28138,7 +28131,7 @@
         <v>23</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>77</v>
@@ -28155,13 +28148,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -28187,13 +28180,13 @@
         <v>188</v>
       </c>
       <c r="M221" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="O221" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="O221" t="s" s="2">
-        <v>881</v>
       </c>
       <c r="P221" s="2"/>
       <c r="Q221" t="s" s="2">
@@ -28222,10 +28215,10 @@
         <v>336</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="AA221" t="s" s="2">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="AB221" t="s" s="2">
         <v>23</v>
@@ -28243,7 +28236,7 @@
         <v>23</v>
       </c>
       <c r="AG221" t="s" s="2">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="AH221" t="s" s="2">
         <v>77</v>
@@ -28260,13 +28253,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -28289,17 +28282,17 @@
         <v>23</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="N222" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="Q222" t="s" s="2">
         <v>23</v>
@@ -28348,7 +28341,7 @@
         <v>23</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>77</v>
@@ -28365,13 +28358,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -28397,10 +28390,10 @@
         <v>188</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -28430,10 +28423,10 @@
         <v>336</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>23</v>
@@ -28451,7 +28444,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -28468,13 +28461,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -28500,10 +28493,10 @@
         <v>312</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -28554,7 +28547,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>77</v>
@@ -28571,13 +28564,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -28674,13 +28667,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28779,13 +28772,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -28884,13 +28877,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28987,13 +28980,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -29090,13 +29083,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -29122,10 +29115,10 @@
         <v>317</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" s="2"/>
@@ -29176,7 +29169,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>77</v>
@@ -29193,13 +29186,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -29296,13 +29289,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -29401,13 +29394,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -29508,13 +29501,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -29540,10 +29533,10 @@
         <v>188</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" s="2"/>
@@ -29573,10 +29566,10 @@
         <v>109</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AA234" t="s" s="2">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AB234" t="s" s="2">
         <v>23</v>
@@ -29594,7 +29587,7 @@
         <v>23</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>77</v>
@@ -29611,13 +29604,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -29640,13 +29633,13 @@
         <v>23</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="M235" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="N235" t="s" s="2">
         <v>914</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" s="2"/>
@@ -29697,7 +29690,7 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>85</v>
@@ -29714,13 +29707,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29743,19 +29736,19 @@
         <v>23</v>
       </c>
       <c r="L236" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="M236" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="N236" t="s" s="2">
         <v>918</v>
       </c>
-      <c r="M236" t="s" s="2">
+      <c r="O236" t="s" s="2">
         <v>919</v>
       </c>
-      <c r="N236" t="s" s="2">
+      <c r="P236" t="s" s="2">
         <v>920</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="P236" t="s" s="2">
-        <v>922</v>
       </c>
       <c r="Q236" t="s" s="2">
         <v>23</v>
@@ -29804,7 +29797,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29821,13 +29814,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29853,13 +29846,13 @@
         <v>188</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
@@ -29888,10 +29881,10 @@
         <v>336</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="AA237" t="s" s="2">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="AB237" t="s" s="2">
         <v>23</v>
@@ -29909,7 +29902,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>77</v>
@@ -29926,7 +29919,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>129</v>
@@ -29958,7 +29951,7 @@
         <v>79</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="N238" t="s" s="2">
         <v>326</v>
@@ -30029,13 +30022,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -30132,13 +30125,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -30235,13 +30228,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -30267,13 +30260,13 @@
         <v>99</v>
       </c>
       <c r="M241" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N241" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N241" t="s" s="2">
+      <c r="O241" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P241" s="2"/>
       <c r="Q241" t="s" s="2">
@@ -30281,7 +30274,7 @@
       </c>
       <c r="R241" s="2"/>
       <c r="S241" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>23</v>
@@ -30323,7 +30316,7 @@
         <v>23</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>85</v>
@@ -30340,13 +30333,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -30372,10 +30365,10 @@
         <v>188</v>
       </c>
       <c r="M242" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N242" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O242" s="2"/>
       <c r="P242" s="2"/>
@@ -30426,7 +30419,7 @@
         <v>23</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>77</v>
@@ -30443,13 +30436,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -30475,10 +30468,10 @@
         <v>79</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -30529,7 +30522,7 @@
         <v>23</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>77</v>
@@ -30541,18 +30534,18 @@
         <v>23</v>
       </c>
       <c r="AK243" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -30651,13 +30644,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -30754,13 +30747,13 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -30859,13 +30852,13 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -30964,13 +30957,13 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" t="s" s="2">
@@ -31069,13 +31062,13 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
@@ -31174,13 +31167,13 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -31209,7 +31202,7 @@
         <v>172</v>
       </c>
       <c r="N250" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O250" t="s" s="2">
         <v>150</v>
@@ -31279,13 +31272,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
@@ -31386,13 +31379,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -31418,14 +31411,14 @@
         <v>154</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="Q252" t="s" s="2">
         <v>23</v>
@@ -31474,7 +31467,7 @@
         <v>23</v>
       </c>
       <c r="AG252" t="s" s="2">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>77</v>
@@ -31491,13 +31484,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -31520,29 +31513,29 @@
         <v>86</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="M253" t="s" s="2">
+        <v>953</v>
+      </c>
+      <c r="N253" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="O253" t="s" s="2">
         <v>955</v>
       </c>
-      <c r="N253" t="s" s="2">
+      <c r="P253" t="s" s="2">
         <v>956</v>
       </c>
-      <c r="O253" t="s" s="2">
+      <c r="Q253" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R253" t="s" s="2">
         <v>957</v>
       </c>
-      <c r="P253" t="s" s="2">
+      <c r="S253" t="s" s="2">
         <v>958</v>
       </c>
-      <c r="Q253" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R253" t="s" s="2">
-        <v>959</v>
-      </c>
-      <c r="S253" t="s" s="2">
-        <v>960</v>
-      </c>
       <c r="T253" t="s" s="2">
         <v>23</v>
       </c>
@@ -31583,7 +31576,7 @@
         <v>23</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="AH253" t="s" s="2">
         <v>77</v>
@@ -31600,13 +31593,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -31629,17 +31622,17 @@
         <v>86</v>
       </c>
       <c r="L254" t="s" s="2">
+        <v>960</v>
+      </c>
+      <c r="M254" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="N254" t="s" s="2">
         <v>962</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>963</v>
-      </c>
-      <c r="N254" t="s" s="2">
-        <v>964</v>
       </c>
       <c r="O254" s="2"/>
       <c r="P254" t="s" s="2">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="Q254" t="s" s="2">
         <v>23</v>
@@ -31688,7 +31681,7 @@
         <v>23</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>85</v>
@@ -31705,13 +31698,13 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -31737,14 +31730,14 @@
         <v>188</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="N255" t="s" s="2">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="Q255" t="s" s="2">
         <v>23</v>
@@ -31772,11 +31765,11 @@
         <v>109</v>
       </c>
       <c r="Z255" t="s" s="2">
+        <v>966</v>
+      </c>
+      <c r="AA255" t="s" s="2">
         <v>968</v>
       </c>
-      <c r="AA255" t="s" s="2">
-        <v>970</v>
-      </c>
       <c r="AB255" t="s" s="2">
         <v>23</v>
       </c>
@@ -31793,7 +31786,7 @@
         <v>23</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="AH255" t="s" s="2">
         <v>77</v>
@@ -31810,13 +31803,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -31913,13 +31906,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -32018,13 +32011,13 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" t="s" s="2">
@@ -32125,13 +32118,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -32157,7 +32150,7 @@
         <v>166</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="N259" t="s" s="2">
         <v>275</v>
@@ -32232,13 +32225,13 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" t="s" s="2">
@@ -32261,17 +32254,17 @@
         <v>86</v>
       </c>
       <c r="L260" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="N260" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="M260" t="s" s="2">
-        <v>978</v>
-      </c>
-      <c r="N260" t="s" s="2">
-        <v>979</v>
       </c>
       <c r="O260" s="2"/>
       <c r="P260" t="s" s="2">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="Q260" t="s" s="2">
         <v>23</v>
@@ -32320,7 +32313,7 @@
         <v>23</v>
       </c>
       <c r="AG260" t="s" s="2">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="AH260" t="s" s="2">
         <v>77</v>
@@ -32337,13 +32330,13 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" t="s" s="2">
@@ -32366,19 +32359,19 @@
         <v>86</v>
       </c>
       <c r="L261" t="s" s="2">
+        <v>980</v>
+      </c>
+      <c r="M261" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="N261" t="s" s="2">
         <v>982</v>
       </c>
-      <c r="M261" t="s" s="2">
+      <c r="O261" t="s" s="2">
         <v>983</v>
       </c>
-      <c r="N261" t="s" s="2">
+      <c r="P261" t="s" s="2">
         <v>984</v>
-      </c>
-      <c r="O261" t="s" s="2">
-        <v>985</v>
-      </c>
-      <c r="P261" t="s" s="2">
-        <v>986</v>
       </c>
       <c r="Q261" t="s" s="2">
         <v>23</v>
@@ -32427,7 +32420,7 @@
         <v>23</v>
       </c>
       <c r="AG261" t="s" s="2">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="AH261" t="s" s="2">
         <v>77</v>
@@ -32444,13 +32437,13 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" t="s" s="2">
@@ -32476,14 +32469,14 @@
         <v>105</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="Q262" t="s" s="2">
         <v>23</v>
@@ -32511,10 +32504,10 @@
         <v>182</v>
       </c>
       <c r="Z262" t="s" s="2">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="AA262" t="s" s="2">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="AB262" t="s" s="2">
         <v>23</v>
@@ -32532,7 +32525,7 @@
         <v>23</v>
       </c>
       <c r="AG262" t="s" s="2">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="AH262" t="s" s="2">
         <v>77</v>
@@ -32549,13 +32542,13 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" t="s" s="2">
@@ -32578,13 +32571,13 @@
         <v>86</v>
       </c>
       <c r="L263" t="s" s="2">
+        <v>992</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>993</v>
+      </c>
+      <c r="N263" t="s" s="2">
         <v>994</v>
-      </c>
-      <c r="M263" t="s" s="2">
-        <v>995</v>
-      </c>
-      <c r="N263" t="s" s="2">
-        <v>996</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" s="2"/>
@@ -32635,7 +32628,7 @@
         <v>23</v>
       </c>
       <c r="AG263" t="s" s="2">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="AH263" t="s" s="2">
         <v>77</v>
@@ -32652,13 +32645,13 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" t="s" s="2">
@@ -32681,17 +32674,17 @@
         <v>86</v>
       </c>
       <c r="L264" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="M264" t="s" s="2">
+        <v>997</v>
+      </c>
+      <c r="N264" t="s" s="2">
         <v>998</v>
-      </c>
-      <c r="M264" t="s" s="2">
-        <v>999</v>
-      </c>
-      <c r="N264" t="s" s="2">
-        <v>1000</v>
       </c>
       <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="Q264" t="s" s="2">
         <v>23</v>
@@ -32740,7 +32733,7 @@
         <v>23</v>
       </c>
       <c r="AG264" t="s" s="2">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="AH264" t="s" s="2">
         <v>77</v>
@@ -32757,13 +32750,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" t="s" s="2">
@@ -32786,17 +32779,17 @@
         <v>23</v>
       </c>
       <c r="L265" t="s" s="2">
+        <v>1001</v>
+      </c>
+      <c r="M265" t="s" s="2">
+        <v>1002</v>
+      </c>
+      <c r="N265" t="s" s="2">
         <v>1003</v>
-      </c>
-      <c r="M265" t="s" s="2">
-        <v>1004</v>
-      </c>
-      <c r="N265" t="s" s="2">
-        <v>1005</v>
       </c>
       <c r="O265" s="2"/>
       <c r="P265" t="s" s="2">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="Q265" t="s" s="2">
         <v>23</v>
@@ -32845,7 +32838,7 @@
         <v>23</v>
       </c>
       <c r="AG265" t="s" s="2">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="AH265" t="s" s="2">
         <v>77</v>
@@ -32862,13 +32855,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" t="s" s="2">
@@ -32894,10 +32887,10 @@
         <v>215</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="O266" s="2"/>
       <c r="P266" s="2"/>
@@ -32948,7 +32941,7 @@
         <v>23</v>
       </c>
       <c r="AG266" t="s" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="AH266" t="s" s="2">
         <v>77</v>
@@ -32965,13 +32958,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" t="s" s="2">
@@ -32997,16 +32990,16 @@
         <v>317</v>
       </c>
       <c r="M267" t="s" s="2">
+        <v>1009</v>
+      </c>
+      <c r="N267" t="s" s="2">
+        <v>1010</v>
+      </c>
+      <c r="O267" t="s" s="2">
         <v>1011</v>
       </c>
-      <c r="N267" t="s" s="2">
+      <c r="P267" t="s" s="2">
         <v>1012</v>
-      </c>
-      <c r="O267" t="s" s="2">
-        <v>1013</v>
-      </c>
-      <c r="P267" t="s" s="2">
-        <v>1014</v>
       </c>
       <c r="Q267" t="s" s="2">
         <v>23</v>
@@ -33055,7 +33048,7 @@
         <v>23</v>
       </c>
       <c r="AG267" t="s" s="2">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="AH267" t="s" s="2">
         <v>77</v>
@@ -33072,13 +33065,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
@@ -33175,13 +33168,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -33280,13 +33273,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -33387,13 +33380,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -33419,16 +33412,16 @@
         <v>188</v>
       </c>
       <c r="M271" t="s" s="2">
+        <v>1017</v>
+      </c>
+      <c r="N271" t="s" s="2">
+        <v>1018</v>
+      </c>
+      <c r="O271" t="s" s="2">
         <v>1019</v>
       </c>
-      <c r="N271" t="s" s="2">
+      <c r="P271" t="s" s="2">
         <v>1020</v>
-      </c>
-      <c r="O271" t="s" s="2">
-        <v>1021</v>
-      </c>
-      <c r="P271" t="s" s="2">
-        <v>1022</v>
       </c>
       <c r="Q271" t="s" s="2">
         <v>23</v>
@@ -33477,7 +33470,7 @@
         <v>23</v>
       </c>
       <c r="AG271" t="s" s="2">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="AH271" t="s" s="2">
         <v>85</v>
@@ -33494,13 +33487,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -33523,19 +33516,19 @@
         <v>23</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="M272" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>1023</v>
+      </c>
+      <c r="O272" t="s" s="2">
         <v>1024</v>
       </c>
-      <c r="N272" t="s" s="2">
+      <c r="P272" t="s" s="2">
         <v>1025</v>
-      </c>
-      <c r="O272" t="s" s="2">
-        <v>1026</v>
-      </c>
-      <c r="P272" t="s" s="2">
-        <v>1027</v>
       </c>
       <c r="Q272" t="s" s="2">
         <v>23</v>
@@ -33584,7 +33577,7 @@
         <v>23</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>77</v>
@@ -33601,7 +33594,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>129</v>
@@ -33704,13 +33697,13 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -33807,13 +33800,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -33910,13 +33903,13 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -33942,13 +33935,13 @@
         <v>99</v>
       </c>
       <c r="M276" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N276" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N276" t="s" s="2">
+      <c r="O276" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O276" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P276" s="2"/>
       <c r="Q276" t="s" s="2">
@@ -33956,7 +33949,7 @@
       </c>
       <c r="R276" s="2"/>
       <c r="S276" t="s" s="2">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="T276" t="s" s="2">
         <v>23</v>
@@ -33998,7 +33991,7 @@
         <v>23</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH276" t="s" s="2">
         <v>85</v>
@@ -34015,13 +34008,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -34044,13 +34037,13 @@
         <v>23</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="M277" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N277" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="N277" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
@@ -34101,7 +34094,7 @@
         <v>23</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>77</v>
@@ -34118,13 +34111,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -34150,13 +34143,13 @@
         <v>79</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="O278" t="s" s="2">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="P278" s="2"/>
       <c r="Q278" t="s" s="2">
@@ -34206,7 +34199,7 @@
         <v>23</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="AH278" t="s" s="2">
         <v>77</v>
@@ -34218,18 +34211,18 @@
         <v>23</v>
       </c>
       <c r="AK278" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -34328,13 +34321,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -34431,13 +34424,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -34536,13 +34529,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -34641,13 +34634,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -34746,13 +34739,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -34851,13 +34844,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
@@ -34886,7 +34879,7 @@
         <v>172</v>
       </c>
       <c r="N285" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O285" t="s" s="2">
         <v>150</v>
@@ -34956,13 +34949,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -35063,13 +35056,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -35095,10 +35088,10 @@
         <v>317</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="O287" s="2"/>
       <c r="P287" s="2"/>
@@ -35149,7 +35142,7 @@
         <v>23</v>
       </c>
       <c r="AG287" t="s" s="2">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AH287" t="s" s="2">
         <v>85</v>
@@ -35166,13 +35159,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -35269,13 +35262,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -35374,13 +35367,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -35481,13 +35474,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -35513,16 +35506,16 @@
         <v>105</v>
       </c>
       <c r="M291" t="s" s="2">
+        <v>1054</v>
+      </c>
+      <c r="N291" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="O291" t="s" s="2">
         <v>1056</v>
       </c>
-      <c r="N291" t="s" s="2">
+      <c r="P291" t="s" s="2">
         <v>1057</v>
-      </c>
-      <c r="O291" t="s" s="2">
-        <v>1058</v>
-      </c>
-      <c r="P291" t="s" s="2">
-        <v>1059</v>
       </c>
       <c r="Q291" t="s" s="2">
         <v>23</v>
@@ -35550,10 +35543,10 @@
         <v>182</v>
       </c>
       <c r="Z291" t="s" s="2">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="AA291" t="s" s="2">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="AB291" t="s" s="2">
         <v>23</v>
@@ -35571,7 +35564,7 @@
         <v>23</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>85</v>
@@ -35588,13 +35581,13 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -35620,14 +35613,14 @@
         <v>105</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="O292" s="2"/>
       <c r="P292" t="s" s="2">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="Q292" t="s" s="2">
         <v>23</v>
@@ -35655,10 +35648,10 @@
         <v>182</v>
       </c>
       <c r="Z292" t="s" s="2">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="AA292" t="s" s="2">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="AB292" t="s" s="2">
         <v>23</v>
@@ -35676,7 +35669,7 @@
         <v>23</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="AH292" t="s" s="2">
         <v>85</v>
@@ -35693,13 +35686,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -35725,13 +35718,13 @@
         <v>188</v>
       </c>
       <c r="M293" t="s" s="2">
+        <v>1067</v>
+      </c>
+      <c r="N293" t="s" s="2">
+        <v>1068</v>
+      </c>
+      <c r="O293" t="s" s="2">
         <v>1069</v>
-      </c>
-      <c r="N293" t="s" s="2">
-        <v>1070</v>
-      </c>
-      <c r="O293" t="s" s="2">
-        <v>1071</v>
       </c>
       <c r="P293" s="2"/>
       <c r="Q293" t="s" s="2">
@@ -35761,7 +35754,7 @@
       </c>
       <c r="Z293" s="2"/>
       <c r="AA293" t="s" s="2">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="AB293" t="s" s="2">
         <v>23</v>
@@ -35779,7 +35772,7 @@
         <v>23</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>77</v>
@@ -35796,13 +35789,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -35828,13 +35821,13 @@
         <v>166</v>
       </c>
       <c r="M294" t="s" s="2">
+        <v>1072</v>
+      </c>
+      <c r="N294" t="s" s="2">
+        <v>1073</v>
+      </c>
+      <c r="O294" t="s" s="2">
         <v>1074</v>
-      </c>
-      <c r="N294" t="s" s="2">
-        <v>1075</v>
-      </c>
-      <c r="O294" t="s" s="2">
-        <v>1076</v>
       </c>
       <c r="P294" s="2"/>
       <c r="Q294" t="s" s="2">
@@ -35884,7 +35877,7 @@
         <v>23</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>77</v>
@@ -35901,13 +35894,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -35933,16 +35926,16 @@
         <v>166</v>
       </c>
       <c r="M295" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="N295" t="s" s="2">
+        <v>1077</v>
+      </c>
+      <c r="O295" t="s" s="2">
         <v>1078</v>
       </c>
-      <c r="N295" t="s" s="2">
+      <c r="P295" t="s" s="2">
         <v>1079</v>
-      </c>
-      <c r="O295" t="s" s="2">
-        <v>1080</v>
-      </c>
-      <c r="P295" t="s" s="2">
-        <v>1081</v>
       </c>
       <c r="Q295" t="s" s="2">
         <v>23</v>
@@ -35991,7 +35984,7 @@
         <v>23</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>77</v>
@@ -36008,13 +36001,13 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -36040,16 +36033,16 @@
         <v>166</v>
       </c>
       <c r="M296" t="s" s="2">
+        <v>1081</v>
+      </c>
+      <c r="N296" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="O296" t="s" s="2">
         <v>1083</v>
       </c>
-      <c r="N296" t="s" s="2">
-        <v>1084</v>
-      </c>
-      <c r="O296" t="s" s="2">
-        <v>1085</v>
-      </c>
       <c r="P296" t="s" s="2">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="Q296" t="s" s="2">
         <v>23</v>
@@ -36098,7 +36091,7 @@
         <v>23</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
